--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B38624-CD32-40FF-B5C9-18E1C2A349CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05878836-FE90-4C95-9BF1-9C1D325777A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="963">
   <si>
     <t>Recensore</t>
   </si>
@@ -3713,15 +3713,15 @@
       </c>
       <c r="F3" s="7">
         <f>+AD6</f>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G3" s="7">
         <f>+AF6</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7">
         <f>+E3-G3</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>10</v>
@@ -3773,15 +3773,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AD6" s="2">
         <f t="shared" ref="AD6:AI6" si="1">SUM(AD8:AD1878)</f>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
@@ -6234,51 +6234,55 @@
       </c>
     </row>
     <row r="28" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
-        <v>0</v>
-      </c>
-      <c r="B28" s="28">
-        <v>1</v>
-      </c>
-      <c r="C28" s="28">
+      <c r="A28" s="31">
+        <v>0</v>
+      </c>
+      <c r="B28" s="31">
+        <v>1</v>
+      </c>
+      <c r="C28" s="31">
         <v>2</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G28" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I28" s="28" t="s">
+      <c r="I28" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="31">
         <v>99</v>
       </c>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="31" t="s">
         <v>328</v>
       </c>
-      <c r="L28" s="28" t="s">
+      <c r="L28" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="29"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="29"/>
+      <c r="N28" s="32" t="s">
+        <v>895</v>
+      </c>
+      <c r="O28" s="33">
+        <v>1</v>
+      </c>
+      <c r="P28" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="32"/>
       <c r="S28" s="2">
         <f t="shared" si="19"/>
         <v>0</v>
@@ -6321,7 +6325,7 @@
       </c>
       <c r="AD28" s="2">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28" s="2">
         <f t="shared" si="30"/>
@@ -6329,7 +6333,7 @@
       </c>
       <c r="AF28" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" s="2">
         <f t="shared" si="4"/>
@@ -11241,51 +11245,55 @@
       </c>
     </row>
     <row r="73" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="28">
-        <v>0</v>
-      </c>
-      <c r="B73" s="28">
-        <v>1</v>
-      </c>
-      <c r="C73" s="28">
+      <c r="A73" s="31">
+        <v>0</v>
+      </c>
+      <c r="B73" s="31">
+        <v>1</v>
+      </c>
+      <c r="C73" s="31">
         <v>6</v>
       </c>
-      <c r="D73" s="29" t="s">
+      <c r="D73" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="E73" s="29" t="s">
+      <c r="E73" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="F73" s="29" t="s">
+      <c r="F73" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="G73" s="29" t="s">
+      <c r="G73" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="H73" s="29" t="s">
+      <c r="H73" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I73" s="28" t="s">
+      <c r="I73" s="31" t="s">
         <v>301</v>
       </c>
-      <c r="J73" s="28">
-        <v>1</v>
-      </c>
-      <c r="K73" s="28" t="s">
+      <c r="J73" s="31">
+        <v>1</v>
+      </c>
+      <c r="K73" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="L73" s="28" t="s">
+      <c r="L73" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="M73" s="29" t="s">
+      <c r="M73" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="N73" s="29"/>
-      <c r="O73" s="30"/>
-      <c r="P73" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="29"/>
+      <c r="N73" s="32" t="s">
+        <v>895</v>
+      </c>
+      <c r="O73" s="33">
+        <v>1</v>
+      </c>
+      <c r="P73" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="32"/>
       <c r="S73" s="2">
         <f t="shared" si="19"/>
         <v>1</v>
@@ -11328,7 +11336,7 @@
       </c>
       <c r="AD73" s="2">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE73" s="2">
         <f t="shared" si="30"/>
@@ -11336,7 +11344,7 @@
       </c>
       <c r="AF73" s="2">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG73" s="2">
         <f t="shared" si="32"/>
@@ -13810,51 +13818,55 @@
       </c>
     </row>
     <row r="96" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="28">
-        <v>0</v>
-      </c>
-      <c r="B96" s="28">
-        <v>1</v>
-      </c>
-      <c r="C96" s="28">
+      <c r="A96" s="31">
+        <v>0</v>
+      </c>
+      <c r="B96" s="31">
+        <v>1</v>
+      </c>
+      <c r="C96" s="31">
         <v>7</v>
       </c>
-      <c r="D96" s="29" t="s">
+      <c r="D96" s="32" t="s">
         <v>571</v>
       </c>
-      <c r="E96" s="29" t="s">
+      <c r="E96" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F96" s="29" t="s">
+      <c r="F96" s="32" t="s">
         <v>586</v>
       </c>
-      <c r="G96" s="29" t="s">
+      <c r="G96" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="H96" s="29" t="s">
+      <c r="H96" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I96" s="28" t="s">
+      <c r="I96" s="31" t="s">
         <v>528</v>
       </c>
-      <c r="J96" s="28">
-        <v>1</v>
-      </c>
-      <c r="K96" s="28" t="s">
+      <c r="J96" s="31">
+        <v>1</v>
+      </c>
+      <c r="K96" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="L96" s="28" t="s">
+      <c r="L96" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="M96" s="29" t="s">
+      <c r="M96" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="N96" s="29"/>
-      <c r="O96" s="30"/>
-      <c r="P96" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q96" s="29"/>
+      <c r="N96" s="32" t="s">
+        <v>895</v>
+      </c>
+      <c r="O96" s="33">
+        <v>1</v>
+      </c>
+      <c r="P96" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q96" s="32"/>
       <c r="S96" s="2">
         <f t="shared" si="35"/>
         <v>1</v>
@@ -13897,7 +13909,7 @@
       </c>
       <c r="AD96" s="2">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE96" s="2">
         <f t="shared" si="46"/>
@@ -13905,7 +13917,7 @@
       </c>
       <c r="AF96" s="2">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG96" s="2">
         <f t="shared" si="32"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05878836-FE90-4C95-9BF1-9C1D325777A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1516D85-B3EA-46FB-993A-F5EE9A81F697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="963">
   <si>
     <t>Recensore</t>
   </si>
@@ -3709,19 +3709,19 @@
       </c>
       <c r="E3" s="7">
         <f>+AH6</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" s="7">
         <f>+AD6</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G3" s="7">
         <f>+AF6</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H3" s="7">
         <f>+E3-G3</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>10</v>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E4" s="9">
         <f>+AI6</f>
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3773,15 +3773,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AD6" s="2">
         <f t="shared" ref="AD6:AI6" si="1">SUM(AD8:AD1878)</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
@@ -3886,11 +3886,11 @@
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI6" s="2">
         <f t="shared" si="1"/>
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:35" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15067,45 +15067,51 @@
       </c>
     </row>
     <row r="107" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="20">
-        <v>0</v>
-      </c>
-      <c r="B107" s="20">
-        <v>1</v>
-      </c>
-      <c r="C107" s="20">
+      <c r="A107" s="31">
+        <v>0</v>
+      </c>
+      <c r="B107" s="31">
+        <v>1</v>
+      </c>
+      <c r="C107" s="31">
         <v>7</v>
       </c>
-      <c r="D107" s="21" t="s">
+      <c r="D107" s="32" t="s">
         <v>948</v>
       </c>
-      <c r="E107" s="21" t="s">
+      <c r="E107" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F107" s="21" t="s">
+      <c r="F107" s="32" t="s">
         <v>949</v>
       </c>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21" t="s">
+      <c r="G107" s="32"/>
+      <c r="H107" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I107" s="20" t="s">
+      <c r="I107" s="31" t="s">
         <v>950</v>
       </c>
-      <c r="J107" s="20"/>
-      <c r="K107" s="20" t="s">
+      <c r="J107" s="31"/>
+      <c r="K107" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="L107" s="20">
+      <c r="L107" s="31">
         <v>30</v>
       </c>
-      <c r="M107" s="21" t="s">
+      <c r="M107" s="32" t="s">
         <v>951</v>
       </c>
-      <c r="N107" s="21"/>
-      <c r="O107" s="7"/>
-      <c r="P107" s="7"/>
-      <c r="Q107" s="21"/>
+      <c r="N107" s="32" t="s">
+        <v>895</v>
+      </c>
+      <c r="O107" s="33">
+        <v>1</v>
+      </c>
+      <c r="P107" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="32"/>
       <c r="S107" s="2">
         <f t="shared" si="35"/>
         <v>0</v>
@@ -15148,7 +15154,7 @@
       </c>
       <c r="AD107" s="2">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE107" s="2">
         <f t="shared" si="46"/>
@@ -15156,7 +15162,7 @@
       </c>
       <c r="AF107" s="2">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG107" s="2">
         <f t="shared" si="32"/>
@@ -15164,11 +15170,11 @@
       </c>
       <c r="AH107" s="2">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI107" s="2">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17654,51 +17660,55 @@
       </c>
     </row>
     <row r="130" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="28">
-        <v>0</v>
-      </c>
-      <c r="B130" s="28">
+      <c r="A130" s="31">
+        <v>0</v>
+      </c>
+      <c r="B130" s="31">
         <v>2</v>
       </c>
-      <c r="C130" s="28">
-        <v>1</v>
-      </c>
-      <c r="D130" s="29" t="s">
+      <c r="C130" s="31">
+        <v>1</v>
+      </c>
+      <c r="D130" s="32" t="s">
         <v>552</v>
       </c>
-      <c r="E130" s="29" t="s">
+      <c r="E130" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="F130" s="29" t="s">
+      <c r="F130" s="32" t="s">
         <v>553</v>
       </c>
-      <c r="G130" s="29" t="s">
+      <c r="G130" s="32" t="s">
         <v>554</v>
       </c>
-      <c r="H130" s="29" t="s">
+      <c r="H130" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I130" s="28" t="s">
+      <c r="I130" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="J130" s="28">
+      <c r="J130" s="31">
         <v>99</v>
       </c>
-      <c r="K130" s="28" t="s">
+      <c r="K130" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="L130" s="28">
+      <c r="L130" s="31">
         <v>8</v>
       </c>
-      <c r="M130" s="29" t="s">
+      <c r="M130" s="32" t="s">
         <v>864</v>
       </c>
-      <c r="N130" s="29"/>
-      <c r="O130" s="30"/>
-      <c r="P130" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q130" s="29"/>
+      <c r="N130" s="32" t="s">
+        <v>895</v>
+      </c>
+      <c r="O130" s="33">
+        <v>1</v>
+      </c>
+      <c r="P130" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q130" s="32"/>
       <c r="S130" s="2">
         <f t="shared" si="35"/>
         <v>0</v>
@@ -17741,7 +17751,7 @@
       </c>
       <c r="AD130" s="2">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE130" s="2">
         <f t="shared" si="46"/>
@@ -17749,7 +17759,7 @@
       </c>
       <c r="AF130" s="2">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG130" s="2">
         <f t="shared" si="32"/>
@@ -17765,51 +17775,55 @@
       </c>
     </row>
     <row r="131" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="28">
-        <v>0</v>
-      </c>
-      <c r="B131" s="28">
+      <c r="A131" s="31">
+        <v>0</v>
+      </c>
+      <c r="B131" s="31">
         <v>2</v>
       </c>
-      <c r="C131" s="28">
-        <v>1</v>
-      </c>
-      <c r="D131" s="29" t="s">
+      <c r="C131" s="31">
+        <v>1</v>
+      </c>
+      <c r="D131" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="E131" s="29" t="s">
+      <c r="E131" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F131" s="29" t="s">
+      <c r="F131" s="32" t="s">
         <v>825</v>
       </c>
-      <c r="G131" s="29" t="s">
+      <c r="G131" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="H131" s="29" t="s">
+      <c r="H131" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I131" s="28" t="s">
+      <c r="I131" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="J131" s="28">
+      <c r="J131" s="31">
         <v>10</v>
       </c>
-      <c r="K131" s="28" t="s">
+      <c r="K131" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="L131" s="28">
+      <c r="L131" s="31">
         <v>5</v>
       </c>
-      <c r="M131" s="29" t="s">
+      <c r="M131" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="N131" s="29"/>
-      <c r="O131" s="30"/>
-      <c r="P131" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q131" s="29"/>
+      <c r="N131" s="32" t="s">
+        <v>895</v>
+      </c>
+      <c r="O131" s="33">
+        <v>1</v>
+      </c>
+      <c r="P131" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q131" s="32"/>
       <c r="S131" s="2">
         <f t="shared" si="35"/>
         <v>0</v>
@@ -17852,7 +17866,7 @@
       </c>
       <c r="AD131" s="2">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE131" s="2">
         <f t="shared" si="46"/>
@@ -17860,7 +17874,7 @@
       </c>
       <c r="AF131" s="2">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG131" s="2">
         <f t="shared" si="32"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1149D8FD-26B3-49E1-826C-CE109AEF864C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2808C3E3-61A6-4D59-8906-2AC8DBC96700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -10458,51 +10458,53 @@
       </c>
     </row>
     <row r="65" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="34">
-        <v>0</v>
-      </c>
-      <c r="B65" s="34">
-        <v>1</v>
-      </c>
-      <c r="C65" s="34">
+      <c r="A65" s="31">
+        <v>0</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1</v>
+      </c>
+      <c r="C65" s="31">
         <v>5</v>
       </c>
-      <c r="D65" s="35" t="s">
+      <c r="D65" s="32" t="s">
         <v>557</v>
       </c>
-      <c r="E65" s="35" t="s">
+      <c r="E65" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="35" t="s">
+      <c r="F65" s="32" t="s">
         <v>558</v>
       </c>
-      <c r="G65" s="35" t="s">
+      <c r="G65" s="32" t="s">
         <v>592</v>
       </c>
-      <c r="H65" s="35" t="s">
+      <c r="H65" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I65" s="34" t="s">
+      <c r="I65" s="31" t="s">
         <v>559</v>
       </c>
-      <c r="J65" s="34">
+      <c r="J65" s="31">
         <v>99</v>
       </c>
-      <c r="K65" s="34" t="s">
+      <c r="K65" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="L65" s="34" t="s">
+      <c r="L65" s="31" t="s">
         <v>597</v>
       </c>
-      <c r="M65" s="35" t="s">
+      <c r="M65" s="32" t="s">
         <v>420</v>
       </c>
-      <c r="N65" s="35" t="s">
-        <v>911</v>
-      </c>
-      <c r="O65" s="36"/>
-      <c r="P65" s="36"/>
-      <c r="Q65" s="35"/>
+      <c r="N65" s="32" t="s">
+        <v>914</v>
+      </c>
+      <c r="O65" s="33">
+        <v>1</v>
+      </c>
+      <c r="P65" s="33"/>
+      <c r="Q65" s="32"/>
       <c r="S65" s="2">
         <f t="shared" si="19"/>
         <v>0</v>
@@ -10549,7 +10551,7 @@
       </c>
       <c r="AE65" s="2">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF65" s="2">
         <f t="shared" si="3"/>
@@ -10557,7 +10559,7 @@
       </c>
       <c r="AG65" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH65" s="2">
         <f t="shared" si="5"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2808C3E3-61A6-4D59-8906-2AC8DBC96700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B193037-C8E8-4583-A705-8FFCAC021923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -9790,49 +9790,51 @@
       </c>
     </row>
     <row r="59" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="34">
-        <v>0</v>
-      </c>
-      <c r="B59" s="34">
-        <v>1</v>
-      </c>
-      <c r="C59" s="34">
+      <c r="A59" s="31">
+        <v>0</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1</v>
+      </c>
+      <c r="C59" s="31">
         <v>5</v>
       </c>
-      <c r="D59" s="35" t="s">
+      <c r="D59" s="32" t="s">
         <v>889</v>
       </c>
-      <c r="E59" s="35" t="s">
+      <c r="E59" s="32" t="s">
         <v>892</v>
       </c>
-      <c r="F59" s="35" t="s">
+      <c r="F59" s="32" t="s">
         <v>890</v>
       </c>
-      <c r="G59" s="35" t="s">
+      <c r="G59" s="32" t="s">
         <v>403</v>
       </c>
-      <c r="H59" s="35" t="s">
+      <c r="H59" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I59" s="34" t="s">
+      <c r="I59" s="31" t="s">
         <v>891</v>
       </c>
-      <c r="J59" s="34"/>
-      <c r="K59" s="34" t="s">
+      <c r="J59" s="31"/>
+      <c r="K59" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="L59" s="34">
+      <c r="L59" s="31">
         <v>55</v>
       </c>
-      <c r="M59" s="35" t="s">
+      <c r="M59" s="32" t="s">
         <v>893</v>
       </c>
-      <c r="N59" s="35" t="s">
-        <v>930</v>
-      </c>
-      <c r="O59" s="36"/>
-      <c r="P59" s="36"/>
-      <c r="Q59" s="35"/>
+      <c r="N59" s="32" t="s">
+        <v>937</v>
+      </c>
+      <c r="O59" s="33">
+        <v>1</v>
+      </c>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="32"/>
       <c r="S59" s="2">
         <f t="shared" si="19"/>
         <v>0</v>
@@ -9879,7 +9881,7 @@
       </c>
       <c r="AE59" s="2">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF59" s="2">
         <f t="shared" si="3"/>
@@ -9887,7 +9889,7 @@
       </c>
       <c r="AG59" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH59" s="2">
         <f t="shared" si="5"/>
@@ -25880,51 +25882,53 @@
       </c>
     </row>
     <row r="203" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="34">
-        <v>0</v>
-      </c>
-      <c r="B203" s="34">
+      <c r="A203" s="31">
+        <v>0</v>
+      </c>
+      <c r="B203" s="31">
         <v>2</v>
       </c>
-      <c r="C203" s="34">
+      <c r="C203" s="31">
         <v>6</v>
       </c>
-      <c r="D203" s="35" t="s">
+      <c r="D203" s="32" t="s">
         <v>534</v>
       </c>
-      <c r="E203" s="35" t="s">
+      <c r="E203" s="32" t="s">
         <v>679</v>
       </c>
-      <c r="F203" s="35" t="s">
+      <c r="F203" s="32" t="s">
         <v>953</v>
       </c>
-      <c r="G203" s="35" t="s">
+      <c r="G203" s="32" t="s">
         <v>584</v>
       </c>
-      <c r="H203" s="35" t="s">
+      <c r="H203" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I203" s="34" t="s">
+      <c r="I203" s="31" t="s">
         <v>535</v>
       </c>
-      <c r="J203" s="34">
+      <c r="J203" s="31">
         <v>2</v>
       </c>
-      <c r="K203" s="34" t="s">
+      <c r="K203" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="L203" s="34" t="s">
+      <c r="L203" s="31" t="s">
         <v>339</v>
       </c>
-      <c r="M203" s="35" t="s">
+      <c r="M203" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="N203" s="35" t="s">
-        <v>899</v>
-      </c>
-      <c r="O203" s="36"/>
-      <c r="P203" s="36"/>
-      <c r="Q203" s="35"/>
+      <c r="N203" s="32" t="s">
+        <v>909</v>
+      </c>
+      <c r="O203" s="33">
+        <v>1</v>
+      </c>
+      <c r="P203" s="33"/>
+      <c r="Q203" s="32"/>
       <c r="S203" s="2">
         <f t="shared" si="51"/>
         <v>0</v>
@@ -25971,7 +25975,7 @@
       </c>
       <c r="AE203" s="2">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF203" s="2">
         <f t="shared" si="63"/>
@@ -25979,7 +25983,7 @@
       </c>
       <c r="AG203" s="2">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH203" s="2">
         <f t="shared" si="65"/>
@@ -25991,51 +25995,53 @@
       </c>
     </row>
     <row r="204" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="34">
-        <v>1</v>
-      </c>
-      <c r="B204" s="34">
+      <c r="A204" s="31">
+        <v>1</v>
+      </c>
+      <c r="B204" s="31">
         <v>2</v>
       </c>
-      <c r="C204" s="34">
+      <c r="C204" s="31">
         <v>6</v>
       </c>
-      <c r="D204" s="35" t="s">
+      <c r="D204" s="32" t="s">
         <v>534</v>
       </c>
-      <c r="E204" s="35" t="s">
+      <c r="E204" s="32" t="s">
         <v>679</v>
       </c>
-      <c r="F204" s="35" t="s">
+      <c r="F204" s="32" t="s">
         <v>954</v>
       </c>
-      <c r="G204" s="35" t="s">
+      <c r="G204" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="H204" s="35" t="s">
+      <c r="H204" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I204" s="34" t="s">
+      <c r="I204" s="31" t="s">
         <v>848</v>
       </c>
-      <c r="J204" s="34">
+      <c r="J204" s="31">
         <v>6</v>
       </c>
-      <c r="K204" s="34" t="s">
+      <c r="K204" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="L204" s="34" t="s">
+      <c r="L204" s="31" t="s">
         <v>339</v>
       </c>
-      <c r="M204" s="35" t="s">
+      <c r="M204" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="N204" s="35" t="s">
-        <v>899</v>
-      </c>
-      <c r="O204" s="36"/>
-      <c r="P204" s="36"/>
-      <c r="Q204" s="35"/>
+      <c r="N204" s="32" t="s">
+        <v>909</v>
+      </c>
+      <c r="O204" s="33">
+        <v>1</v>
+      </c>
+      <c r="P204" s="33"/>
+      <c r="Q204" s="32"/>
       <c r="S204" s="2">
         <f t="shared" si="51"/>
         <v>0</v>
@@ -26082,7 +26088,7 @@
       </c>
       <c r="AE204" s="2">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF204" s="2">
         <f t="shared" si="63"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B193037-C8E8-4583-A705-8FFCAC021923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E5AF74-0E5E-4FB0-87ED-A7AD18B9D7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -5784,51 +5784,53 @@
       </c>
     </row>
     <row r="23" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="34">
-        <v>0</v>
-      </c>
-      <c r="B23" s="34">
-        <v>1</v>
-      </c>
-      <c r="C23" s="34">
+      <c r="A23" s="31">
+        <v>0</v>
+      </c>
+      <c r="B23" s="31">
+        <v>1</v>
+      </c>
+      <c r="C23" s="31">
         <v>2</v>
       </c>
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="32" t="s">
         <v>764</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="32" t="s">
         <v>765</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="32" t="s">
         <v>458</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H23" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I23" s="34" t="s">
+      <c r="I23" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="J23" s="34">
+      <c r="J23" s="31">
         <v>99</v>
       </c>
-      <c r="K23" s="34" t="s">
+      <c r="K23" s="31" t="s">
         <v>698</v>
       </c>
-      <c r="L23" s="34" t="s">
+      <c r="L23" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="M23" s="35" t="s">
+      <c r="M23" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="N23" s="35" t="s">
-        <v>897</v>
-      </c>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="35"/>
+      <c r="N23" s="32" t="s">
+        <v>908</v>
+      </c>
+      <c r="O23" s="33">
+        <v>1</v>
+      </c>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="32"/>
       <c r="S23" s="2">
         <f t="shared" si="19"/>
         <v>0</v>
@@ -5875,7 +5877,7 @@
       </c>
       <c r="AE23" s="2">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" s="2">
         <f t="shared" si="3"/>
@@ -5883,7 +5885,7 @@
       </c>
       <c r="AG23" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" s="2">
         <f t="shared" si="5"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E5AF74-0E5E-4FB0-87ED-A7AD18B9D7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27464295-426D-45B4-B746-17B01277F85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -6678,51 +6678,53 @@
       </c>
     </row>
     <row r="31" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="34">
-        <v>0</v>
-      </c>
-      <c r="B31" s="34">
-        <v>1</v>
-      </c>
-      <c r="C31" s="34">
+      <c r="A31" s="31">
+        <v>0</v>
+      </c>
+      <c r="B31" s="31">
+        <v>1</v>
+      </c>
+      <c r="C31" s="31">
         <v>2</v>
       </c>
-      <c r="D31" s="35" t="s">
+      <c r="D31" s="32" t="s">
         <v>347</v>
       </c>
-      <c r="E31" s="35" t="s">
+      <c r="E31" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="32" t="s">
         <v>364</v>
       </c>
-      <c r="G31" s="35" t="s">
+      <c r="G31" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H31" s="35" t="s">
+      <c r="H31" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I31" s="34" t="s">
+      <c r="I31" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="31">
         <v>99</v>
       </c>
-      <c r="K31" s="34" t="s">
+      <c r="K31" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="31">
         <v>90</v>
       </c>
-      <c r="M31" s="35" t="s">
+      <c r="M31" s="32" t="s">
         <v>907</v>
       </c>
-      <c r="N31" s="35" t="s">
-        <v>911</v>
-      </c>
-      <c r="O31" s="36"/>
-      <c r="P31" s="36"/>
-      <c r="Q31" s="35"/>
+      <c r="N31" s="32" t="s">
+        <v>914</v>
+      </c>
+      <c r="O31" s="33">
+        <v>1</v>
+      </c>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="32"/>
       <c r="S31" s="2">
         <f t="shared" si="19"/>
         <v>0</v>
@@ -6769,7 +6771,7 @@
       </c>
       <c r="AE31" s="2">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" s="2">
         <f t="shared" si="3"/>
@@ -6777,7 +6779,7 @@
       </c>
       <c r="AG31" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" s="2">
         <f t="shared" si="5"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27464295-426D-45B4-B746-17B01277F85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AE74EB-58D5-4974-BC16-90F46887F634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -10690,51 +10690,53 @@
       </c>
     </row>
     <row r="67" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="34">
-        <v>0</v>
-      </c>
-      <c r="B67" s="34">
-        <v>1</v>
-      </c>
-      <c r="C67" s="34">
+      <c r="A67" s="31">
+        <v>0</v>
+      </c>
+      <c r="B67" s="31">
+        <v>1</v>
+      </c>
+      <c r="C67" s="31">
         <v>5</v>
       </c>
-      <c r="D67" s="35" t="s">
+      <c r="D67" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="E67" s="35" t="s">
+      <c r="E67" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="F67" s="35" t="s">
+      <c r="F67" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="G67" s="35" t="s">
+      <c r="G67" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="H67" s="35" t="s">
+      <c r="H67" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I67" s="34" t="s">
+      <c r="I67" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="J67" s="34">
+      <c r="J67" s="31">
         <v>3</v>
       </c>
-      <c r="K67" s="34" t="s">
+      <c r="K67" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="L67" s="34" t="s">
+      <c r="L67" s="31" t="s">
         <v>335</v>
       </c>
-      <c r="M67" s="35" t="s">
+      <c r="M67" s="32" t="s">
         <v>496</v>
       </c>
-      <c r="N67" s="35" t="s">
-        <v>931</v>
-      </c>
-      <c r="O67" s="36"/>
-      <c r="P67" s="36"/>
-      <c r="Q67" s="35"/>
+      <c r="N67" s="32" t="s">
+        <v>932</v>
+      </c>
+      <c r="O67" s="33">
+        <v>1</v>
+      </c>
+      <c r="P67" s="33"/>
+      <c r="Q67" s="32"/>
       <c r="S67" s="2">
         <f t="shared" si="19"/>
         <v>0</v>
@@ -10781,7 +10783,7 @@
       </c>
       <c r="AE67" s="2">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF67" s="2">
         <f t="shared" si="3"/>
@@ -10789,7 +10791,7 @@
       </c>
       <c r="AG67" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH67" s="2">
         <f t="shared" si="5"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AE74EB-58D5-4974-BC16-90F46887F634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34C2CC7-0FAC-459A-8194-3A03A58320FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -22788,51 +22788,53 @@
       </c>
     </row>
     <row r="175" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="34">
-        <v>0</v>
-      </c>
-      <c r="B175" s="34">
+      <c r="A175" s="31">
+        <v>0</v>
+      </c>
+      <c r="B175" s="31">
         <v>2</v>
       </c>
-      <c r="C175" s="34">
+      <c r="C175" s="31">
         <v>4</v>
       </c>
-      <c r="D175" s="35" t="s">
+      <c r="D175" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="E175" s="35" t="s">
+      <c r="E175" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="F175" s="35" t="s">
+      <c r="F175" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="G175" s="35" t="s">
+      <c r="G175" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H175" s="35" t="s">
+      <c r="H175" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I175" s="34" t="s">
+      <c r="I175" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="J175" s="34">
+      <c r="J175" s="31">
         <v>4</v>
       </c>
-      <c r="K175" s="34" t="s">
+      <c r="K175" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="L175" s="34" t="s">
+      <c r="L175" s="31" t="s">
         <v>855</v>
       </c>
-      <c r="M175" s="35" t="s">
+      <c r="M175" s="32" t="s">
         <v>747</v>
       </c>
-      <c r="N175" s="35" t="s">
-        <v>931</v>
-      </c>
-      <c r="O175" s="36"/>
-      <c r="P175" s="36"/>
-      <c r="Q175" s="35"/>
+      <c r="N175" s="32" t="s">
+        <v>932</v>
+      </c>
+      <c r="O175" s="33">
+        <v>1</v>
+      </c>
+      <c r="P175" s="33"/>
+      <c r="Q175" s="32"/>
       <c r="S175" s="2">
         <f t="shared" si="51"/>
         <v>0</v>
@@ -22879,7 +22881,7 @@
       </c>
       <c r="AE175" s="2">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF175" s="2">
         <f t="shared" si="47"/>
@@ -22887,7 +22889,7 @@
       </c>
       <c r="AG175" s="2">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH175" s="2">
         <f t="shared" si="49"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34C2CC7-0FAC-459A-8194-3A03A58320FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E0796C-6D26-49D4-95E0-EBBB44DC6BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tavole e pause golose'!$A$7:$AI$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tavole e pause golose'!$A$7:$AI$235</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Tavole e pause golose'!$B$7:$I$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -22677,51 +22677,53 @@
       </c>
     </row>
     <row r="174" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="34">
-        <v>0</v>
-      </c>
-      <c r="B174" s="34">
+      <c r="A174" s="31">
+        <v>0</v>
+      </c>
+      <c r="B174" s="31">
         <v>2</v>
       </c>
-      <c r="C174" s="34">
+      <c r="C174" s="31">
         <v>4</v>
       </c>
-      <c r="D174" s="35" t="s">
+      <c r="D174" s="32" t="s">
         <v>546</v>
       </c>
-      <c r="E174" s="35" t="s">
+      <c r="E174" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="F174" s="35" t="s">
+      <c r="F174" s="32" t="s">
         <v>407</v>
       </c>
-      <c r="G174" s="35" t="s">
+      <c r="G174" s="32" t="s">
         <v>405</v>
       </c>
-      <c r="H174" s="35" t="s">
+      <c r="H174" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I174" s="34" t="s">
+      <c r="I174" s="31" t="s">
         <v>547</v>
       </c>
-      <c r="J174" s="34">
+      <c r="J174" s="31">
         <v>99</v>
       </c>
-      <c r="K174" s="34" t="s">
+      <c r="K174" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="L174" s="34">
+      <c r="L174" s="31">
         <v>35</v>
       </c>
-      <c r="M174" s="35" t="s">
+      <c r="M174" s="32" t="s">
         <v>928</v>
       </c>
-      <c r="N174" s="35" t="s">
-        <v>930</v>
-      </c>
-      <c r="O174" s="36"/>
-      <c r="P174" s="36"/>
-      <c r="Q174" s="35"/>
+      <c r="N174" s="32" t="s">
+        <v>937</v>
+      </c>
+      <c r="O174" s="33">
+        <v>1</v>
+      </c>
+      <c r="P174" s="33"/>
+      <c r="Q174" s="32"/>
       <c r="S174" s="2">
         <f t="shared" si="51"/>
         <v>0</v>
@@ -22768,7 +22770,7 @@
       </c>
       <c r="AE174" s="2">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF174" s="2">
         <f t="shared" si="47"/>
@@ -22776,7 +22778,7 @@
       </c>
       <c r="AG174" s="2">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH174" s="2">
         <f t="shared" si="49"/>
@@ -27135,51 +27137,53 @@
       </c>
     </row>
     <row r="214" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="34">
-        <v>0</v>
-      </c>
-      <c r="B214" s="34">
+      <c r="A214" s="31">
+        <v>0</v>
+      </c>
+      <c r="B214" s="31">
         <v>2</v>
       </c>
-      <c r="C214" s="34">
+      <c r="C214" s="31">
         <v>7</v>
       </c>
-      <c r="D214" s="35" t="s">
+      <c r="D214" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="E214" s="35" t="s">
+      <c r="E214" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F214" s="35" t="s">
+      <c r="F214" s="32" t="s">
         <v>822</v>
       </c>
-      <c r="G214" s="35" t="s">
+      <c r="G214" s="32" t="s">
         <v>578</v>
       </c>
-      <c r="H214" s="35" t="s">
+      <c r="H214" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I214" s="34" t="s">
+      <c r="I214" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="J214" s="34">
+      <c r="J214" s="31">
         <v>99</v>
       </c>
-      <c r="K214" s="34" t="s">
+      <c r="K214" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="L214" s="34" t="s">
+      <c r="L214" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="M214" s="35" t="s">
+      <c r="M214" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="N214" s="35" t="s">
-        <v>930</v>
-      </c>
-      <c r="O214" s="36"/>
-      <c r="P214" s="36"/>
-      <c r="Q214" s="35"/>
+      <c r="N214" s="32" t="s">
+        <v>937</v>
+      </c>
+      <c r="O214" s="33">
+        <v>1</v>
+      </c>
+      <c r="P214" s="33"/>
+      <c r="Q214" s="32"/>
       <c r="S214" s="2">
         <f t="shared" si="67"/>
         <v>0</v>
@@ -27226,7 +27230,7 @@
       </c>
       <c r="AE214" s="2">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF214" s="2">
         <f t="shared" si="63"/>
@@ -27234,7 +27238,7 @@
       </c>
       <c r="AG214" s="2">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH214" s="2">
         <f t="shared" si="65"/>
@@ -33435,7 +33439,7 @@
       <c r="Q437" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:AI228" xr:uid="{11EDAB9D-D4E1-484F-984E-C23E0F5BA036}">
+  <autoFilter ref="A7:AI235" xr:uid="{11EDAB9D-D4E1-484F-984E-C23E0F5BA036}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AI164">
       <sortCondition ref="J7:J151"/>
     </sortState>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E0796C-6D26-49D4-95E0-EBBB44DC6BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B47150A-54B6-4C4A-B8DF-59D1EB936594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
   <sheets>
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
@@ -3749,43 +3749,43 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI437"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="6.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="2" customWidth="1"/>
-    <col min="10" max="11" width="8.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" style="2" customWidth="1"/>
+    <col min="2" max="3" width="6.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="35.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" style="2" customWidth="1"/>
+    <col min="10" max="11" width="8.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" style="14" customWidth="1"/>
     <col min="13" max="13" width="29" style="15" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" style="2" customWidth="1"/>
     <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.42578125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.28515625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.28515625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" style="2" customWidth="1"/>
-    <col min="22" max="27" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.44140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.33203125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="2" customWidth="1"/>
+    <col min="22" max="27" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.85546875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="27.28515625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="19.85546875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="15.140625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="18.140625" style="2" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="3"/>
+    <col min="30" max="30" width="21.88671875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="27.33203125" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.33203125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="19.88671875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.109375" style="2" customWidth="1"/>
+    <col min="35" max="35" width="18.109375" style="2" customWidth="1"/>
+    <col min="36" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="17" t="s">
         <v>8</v>
       </c>
@@ -3808,7 +3808,7 @@
       <c r="K2" s="6"/>
       <c r="N2" s="22"/>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D4" s="18" t="s">
         <v>3</v>
       </c>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3868,7 +3868,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="19" t="s">
         <v>12</v>
       </c>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3941,7 +3941,7 @@
       <c r="AF5" s="12"/>
       <c r="AG5" s="12"/>
     </row>
-    <row r="6" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F6" s="2"/>
       <c r="S6" s="2" t="s">
         <v>15</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3998,7 +3998,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:35" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
         <v>707</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>0</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
         <v>0</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
         <v>0</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>0</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>0</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>0</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="31">
         <v>0</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>0</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20">
         <v>0</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>0</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="31">
         <v>0</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>0</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
         <v>0</v>
       </c>
@@ -5561,7 +5561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>0</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>0</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="31">
         <v>0</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>0</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>0</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20">
         <v>0</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="31">
         <v>0</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="31">
         <v>0</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>0</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>0</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="31">
         <v>0</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="34">
         <v>0</v>
       </c>
@@ -6901,7 +6901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20">
         <v>0</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="31">
         <v>0</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="31">
         <v>0</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20">
         <v>0</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>0</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="31">
         <v>0</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20">
         <v>0</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="31">
         <v>0</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="34">
         <v>0</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="34">
         <v>0</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="31">
         <v>0</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="34">
         <v>0</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="31">
         <v>0</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="34">
         <v>0</v>
       </c>
@@ -8465,7 +8465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="34">
         <v>0</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="34">
         <v>0</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="31">
         <v>0</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="28">
         <v>0</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="34">
         <v>0</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="34">
         <v>0</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20">
         <v>0</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="34">
         <v>0</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="20">
         <v>0</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="31">
         <v>0</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="34">
         <v>0</v>
       </c>
@@ -9684,7 +9684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="20">
         <v>0</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="31">
         <v>0</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="31">
         <v>0</v>
       </c>
@@ -10015,7 +10015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="20">
         <v>0</v>
       </c>
@@ -10124,7 +10124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="31">
         <v>0</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="31">
         <v>0</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="31">
         <v>0</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="31">
         <v>0</v>
       </c>
@@ -10576,7 +10576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="31">
         <v>0</v>
       </c>
@@ -10689,7 +10689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="31">
         <v>0</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="20">
         <v>0</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="34">
         <v>0</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="34">
         <v>0</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20">
         <v>0</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="20">
         <v>1</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="31">
         <v>0</v>
       </c>
@@ -11466,7 +11466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="31">
         <v>0</v>
       </c>
@@ -11581,7 +11581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="31">
         <v>0</v>
       </c>
@@ -11692,7 +11692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="31">
         <v>1</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="31">
         <v>0</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="31">
         <v>0</v>
       </c>
@@ -12029,7 +12029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="31">
         <v>0</v>
       </c>
@@ -12144,7 +12144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="34">
         <v>0</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="28">
         <v>0</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="31">
         <v>0</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="34">
         <v>0</v>
       </c>
@@ -12590,7 +12590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="31">
         <v>0</v>
       </c>
@@ -12703,7 +12703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="20">
         <v>0</v>
       </c>
@@ -12810,7 +12810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="28">
         <v>0</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="20">
         <v>0</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="34">
         <v>0</v>
       </c>
@@ -13139,7 +13139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="31">
         <v>0</v>
       </c>
@@ -13252,7 +13252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="41">
         <v>0</v>
       </c>
@@ -13357,7 +13357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="20">
         <v>0</v>
       </c>
@@ -13466,7 +13466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="31">
         <v>0</v>
       </c>
@@ -13579,7 +13579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="31">
         <v>1</v>
       </c>
@@ -13692,7 +13692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="31">
         <v>1</v>
       </c>
@@ -13805,7 +13805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="31">
         <v>1</v>
       </c>
@@ -13918,7 +13918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="31">
         <v>1</v>
       </c>
@@ -14031,7 +14031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="31">
         <v>1</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="31">
         <v>0</v>
       </c>
@@ -14259,7 +14259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="31">
         <v>0</v>
       </c>
@@ -14372,7 +14372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="31">
         <v>0</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="31">
         <v>1</v>
       </c>
@@ -14598,7 +14598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="31">
         <v>1</v>
       </c>
@@ -14711,7 +14711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="31">
         <v>0</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="31">
         <v>1</v>
       </c>
@@ -14941,7 +14941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="31">
         <v>1</v>
       </c>
@@ -15056,7 +15056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="31">
         <v>1</v>
       </c>
@@ -15171,7 +15171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="34">
         <v>0</v>
       </c>
@@ -15282,7 +15282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="34">
         <v>1</v>
       </c>
@@ -15393,7 +15393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="31">
         <v>0</v>
       </c>
@@ -15504,7 +15504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="20">
         <v>0</v>
       </c>
@@ -15609,7 +15609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="34">
         <v>0</v>
       </c>
@@ -15720,7 +15720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="31">
         <v>0</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="31">
         <v>1</v>
       </c>
@@ -15944,7 +15944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="20">
         <v>0</v>
       </c>
@@ -16051,7 +16051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="31">
         <v>0</v>
       </c>
@@ -16166,7 +16166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="31">
         <v>1</v>
       </c>
@@ -16281,7 +16281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="20">
         <v>0</v>
       </c>
@@ -16390,7 +16390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="31">
         <v>0</v>
       </c>
@@ -16505,7 +16505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="31">
         <v>0</v>
       </c>
@@ -16620,7 +16620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="31">
         <v>1</v>
       </c>
@@ -16735,7 +16735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="31">
         <v>1</v>
       </c>
@@ -16850,7 +16850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="31">
         <v>1</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="31">
         <v>1</v>
       </c>
@@ -17080,7 +17080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="31">
         <v>0</v>
       </c>
@@ -17193,7 +17193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="31">
         <v>0</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="31">
         <v>0</v>
       </c>
@@ -17417,7 +17417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="31">
         <v>0</v>
       </c>
@@ -17532,7 +17532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="31">
         <v>1</v>
       </c>
@@ -17647,7 +17647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="31">
         <v>1</v>
       </c>
@@ -17762,7 +17762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="41">
         <v>0</v>
       </c>
@@ -17865,7 +17865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="34">
         <v>0</v>
       </c>
@@ -17976,7 +17976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="20">
         <v>0</v>
       </c>
@@ -18085,7 +18085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="31">
         <v>0</v>
       </c>
@@ -18192,7 +18192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="31">
         <v>0</v>
       </c>
@@ -18301,7 +18301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="31">
         <v>0</v>
       </c>
@@ -18416,7 +18416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="31">
         <v>0</v>
       </c>
@@ -18531,7 +18531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="31">
         <v>0</v>
       </c>
@@ -18644,7 +18644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="31">
         <v>1</v>
       </c>
@@ -18757,7 +18757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="31">
         <v>0</v>
       </c>
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="31">
         <v>0</v>
       </c>
@@ -18987,7 +18987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="31">
         <v>0</v>
       </c>
@@ -19102,7 +19102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="31">
         <v>0</v>
       </c>
@@ -19215,7 +19215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="31">
         <v>1</v>
       </c>
@@ -19328,7 +19328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="31">
         <v>0</v>
       </c>
@@ -19439,7 +19439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="31">
         <v>0</v>
       </c>
@@ -19554,7 +19554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="31">
         <v>0</v>
       </c>
@@ -19669,7 +19669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="31">
         <v>0</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="31">
         <v>0</v>
       </c>
@@ -19895,7 +19895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="20">
         <v>0</v>
       </c>
@@ -20004,7 +20004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="31">
         <v>0</v>
       </c>
@@ -20117,7 +20117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="34">
         <v>0</v>
       </c>
@@ -20226,7 +20226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="31">
         <v>0</v>
       </c>
@@ -20339,7 +20339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="31">
         <v>0</v>
       </c>
@@ -20454,7 +20454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="31">
         <v>1</v>
       </c>
@@ -20567,7 +20567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="31">
         <v>0</v>
       </c>
@@ -20680,7 +20680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="31">
         <v>1</v>
       </c>
@@ -20793,7 +20793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="31">
         <v>0</v>
       </c>
@@ -20906,7 +20906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="34">
         <v>0</v>
       </c>
@@ -21017,7 +21017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="28">
         <v>0</v>
       </c>
@@ -21128,7 +21128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="41">
         <v>0</v>
       </c>
@@ -21233,7 +21233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="28">
         <v>0</v>
       </c>
@@ -21336,7 +21336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="34">
         <v>0</v>
       </c>
@@ -21447,7 +21447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="31">
         <v>0</v>
       </c>
@@ -21560,7 +21560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="34">
         <v>0</v>
       </c>
@@ -21671,7 +21671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="34">
         <v>0</v>
       </c>
@@ -21782,7 +21782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="28">
         <v>0</v>
       </c>
@@ -21893,7 +21893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="31">
         <v>0</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="31">
         <v>0</v>
       </c>
@@ -22123,7 +22123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="31">
         <v>1</v>
       </c>
@@ -22238,7 +22238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="20">
         <v>0</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="31">
         <v>0</v>
       </c>
@@ -22462,7 +22462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="31">
         <v>0</v>
       </c>
@@ -22567,7 +22567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="20">
         <v>0</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="31">
         <v>0</v>
       </c>
@@ -22789,7 +22789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="31">
         <v>0</v>
       </c>
@@ -22902,7 +22902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="34">
         <v>0</v>
       </c>
@@ -23013,7 +23013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="34">
         <v>0</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="34">
         <v>1</v>
       </c>
@@ -23235,7 +23235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="34">
         <v>1</v>
       </c>
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="20">
         <v>0</v>
       </c>
@@ -23451,7 +23451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="20">
         <v>0</v>
       </c>
@@ -23560,7 +23560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="34">
         <v>0</v>
       </c>
@@ -23671,7 +23671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="20">
         <v>0</v>
       </c>
@@ -23780,7 +23780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="20">
         <v>0</v>
       </c>
@@ -23889,7 +23889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="34">
         <v>0</v>
       </c>
@@ -24000,7 +24000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="31">
         <v>0</v>
       </c>
@@ -24111,7 +24111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="34">
         <v>0</v>
       </c>
@@ -24222,7 +24222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="34">
         <v>0</v>
       </c>
@@ -24333,7 +24333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="34">
         <v>0</v>
       </c>
@@ -24444,7 +24444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="34">
         <v>0</v>
       </c>
@@ -24555,7 +24555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="34">
         <v>0</v>
       </c>
@@ -24666,7 +24666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="31">
         <v>0</v>
       </c>
@@ -24779,7 +24779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="31">
         <v>0</v>
       </c>
@@ -24894,7 +24894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="20">
         <v>0</v>
       </c>
@@ -25003,7 +25003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="34">
         <v>0</v>
       </c>
@@ -25114,7 +25114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="34">
         <v>0</v>
       </c>
@@ -25225,7 +25225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="34">
         <v>0</v>
       </c>
@@ -25336,7 +25336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="34">
         <v>0</v>
       </c>
@@ -25447,7 +25447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="34">
         <v>0</v>
       </c>
@@ -25558,7 +25558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="31">
         <v>0</v>
       </c>
@@ -25671,7 +25671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="34">
         <v>0</v>
       </c>
@@ -25782,7 +25782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="34">
         <v>0</v>
       </c>
@@ -25891,7 +25891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="31">
         <v>0</v>
       </c>
@@ -26004,7 +26004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="31">
         <v>1</v>
       </c>
@@ -26117,7 +26117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="31">
         <v>0</v>
       </c>
@@ -26232,7 +26232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="31">
         <v>0</v>
       </c>
@@ -26343,7 +26343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="31">
         <v>0</v>
       </c>
@@ -26456,7 +26456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="34">
         <v>0</v>
       </c>
@@ -26567,7 +26567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="31">
         <v>0</v>
       </c>
@@ -26682,7 +26682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="31">
         <v>0</v>
       </c>
@@ -26797,7 +26797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="31">
         <v>0</v>
       </c>
@@ -26910,7 +26910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="31">
         <v>1</v>
       </c>
@@ -27023,7 +27023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="31">
         <v>0</v>
       </c>
@@ -27136,7 +27136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="31">
         <v>0</v>
       </c>
@@ -27249,52 +27249,54 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="34">
-        <v>0</v>
-      </c>
-      <c r="B215" s="34">
+    <row r="215" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="31">
+        <v>0</v>
+      </c>
+      <c r="B215" s="31">
         <v>2</v>
       </c>
-      <c r="C215" s="34">
+      <c r="C215" s="31">
         <v>7</v>
       </c>
-      <c r="D215" s="35" t="s">
+      <c r="D215" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="E215" s="35" t="s">
+      <c r="E215" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F215" s="35" t="s">
+      <c r="F215" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="G215" s="35" t="s">
+      <c r="G215" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="H215" s="35" t="s">
+      <c r="H215" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I215" s="34" t="s">
+      <c r="I215" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="J215" s="34">
+      <c r="J215" s="31">
         <v>6</v>
       </c>
-      <c r="K215" s="34" t="s">
+      <c r="K215" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="L215" s="34" t="s">
+      <c r="L215" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="M215" s="35" t="s">
+      <c r="M215" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="N215" s="35" t="s">
-        <v>897</v>
-      </c>
-      <c r="O215" s="36"/>
-      <c r="P215" s="36"/>
-      <c r="Q215" s="35"/>
+      <c r="N215" s="32" t="s">
+        <v>908</v>
+      </c>
+      <c r="O215" s="33">
+        <v>1</v>
+      </c>
+      <c r="P215" s="33"/>
+      <c r="Q215" s="32"/>
       <c r="S215" s="2">
         <f t="shared" si="67"/>
         <v>0</v>
@@ -27341,7 +27343,7 @@
       </c>
       <c r="AE215" s="2">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF215" s="2">
         <f t="shared" si="63"/>
@@ -27349,7 +27351,7 @@
       </c>
       <c r="AG215" s="2">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH215" s="2">
         <f t="shared" si="65"/>
@@ -27360,52 +27362,54 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="34">
-        <v>1</v>
-      </c>
-      <c r="B216" s="34">
+    <row r="216" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="31">
+        <v>1</v>
+      </c>
+      <c r="B216" s="31">
         <v>2</v>
       </c>
-      <c r="C216" s="34">
+      <c r="C216" s="31">
         <v>7</v>
       </c>
-      <c r="D216" s="35" t="s">
+      <c r="D216" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="E216" s="35" t="s">
+      <c r="E216" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F216" s="35" t="s">
+      <c r="F216" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="G216" s="35" t="s">
+      <c r="G216" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="H216" s="35" t="s">
+      <c r="H216" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I216" s="34" t="s">
+      <c r="I216" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="J216" s="34">
+      <c r="J216" s="31">
         <v>4</v>
       </c>
-      <c r="K216" s="34" t="s">
+      <c r="K216" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="L216" s="34" t="s">
+      <c r="L216" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="M216" s="35" t="s">
+      <c r="M216" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="N216" s="35" t="s">
-        <v>897</v>
-      </c>
-      <c r="O216" s="36"/>
-      <c r="P216" s="36"/>
-      <c r="Q216" s="35"/>
+      <c r="N216" s="32" t="s">
+        <v>908</v>
+      </c>
+      <c r="O216" s="33">
+        <v>1</v>
+      </c>
+      <c r="P216" s="33"/>
+      <c r="Q216" s="32"/>
       <c r="S216" s="2">
         <f t="shared" si="67"/>
         <v>0</v>
@@ -27452,7 +27456,7 @@
       </c>
       <c r="AE216" s="2">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF216" s="2">
         <f t="shared" si="63"/>
@@ -27471,7 +27475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="31">
         <v>0</v>
       </c>
@@ -27584,7 +27588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="34">
         <v>0</v>
       </c>
@@ -27695,7 +27699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="34">
         <v>0</v>
       </c>
@@ -27806,7 +27810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="34">
         <v>0</v>
       </c>
@@ -27917,7 +27921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="31">
         <v>0</v>
       </c>
@@ -28030,7 +28034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="31">
         <v>0</v>
       </c>
@@ -28143,7 +28147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="31">
         <v>0</v>
       </c>
@@ -28254,7 +28258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="31">
         <v>1</v>
       </c>
@@ -28361,7 +28365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="31">
         <v>0</v>
       </c>
@@ -28474,7 +28478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="31">
         <v>1</v>
       </c>
@@ -28589,7 +28593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="31">
         <v>0</v>
       </c>
@@ -28702,7 +28706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="31">
         <v>1</v>
       </c>
@@ -28815,7 +28819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="31">
         <v>1</v>
       </c>
@@ -28928,7 +28932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="31">
         <v>0</v>
       </c>
@@ -29041,7 +29045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="31">
         <v>1</v>
       </c>
@@ -29154,7 +29158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="31">
         <v>0</v>
       </c>
@@ -29267,7 +29271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="34">
         <v>0</v>
       </c>
@@ -29378,7 +29382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="34">
         <v>1</v>
       </c>
@@ -29489,7 +29493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="34">
         <v>1</v>
       </c>
@@ -29600,7 +29604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="20"/>
       <c r="B236" s="20"/>
       <c r="C236" s="20"/>
@@ -29619,7 +29623,7 @@
       <c r="P236" s="20"/>
       <c r="Q236" s="21"/>
     </row>
-    <row r="237" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="20"/>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -29638,7 +29642,7 @@
       <c r="P237" s="20"/>
       <c r="Q237" s="21"/>
     </row>
-    <row r="238" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="20"/>
       <c r="B238" s="20"/>
       <c r="C238" s="20"/>
@@ -29657,7 +29661,7 @@
       <c r="P238" s="20"/>
       <c r="Q238" s="21"/>
     </row>
-    <row r="239" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="20"/>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -29676,7 +29680,7 @@
       <c r="P239" s="20"/>
       <c r="Q239" s="21"/>
     </row>
-    <row r="240" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="20"/>
@@ -29695,7 +29699,7 @@
       <c r="P240" s="20"/>
       <c r="Q240" s="21"/>
     </row>
-    <row r="241" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="20"/>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -29714,7 +29718,7 @@
       <c r="P241" s="20"/>
       <c r="Q241" s="21"/>
     </row>
-    <row r="242" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="20"/>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -29733,7 +29737,7 @@
       <c r="P242" s="20"/>
       <c r="Q242" s="21"/>
     </row>
-    <row r="243" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="20"/>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -29752,7 +29756,7 @@
       <c r="P243" s="20"/>
       <c r="Q243" s="21"/>
     </row>
-    <row r="244" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="20"/>
       <c r="B244" s="20"/>
       <c r="C244" s="20"/>
@@ -29771,7 +29775,7 @@
       <c r="P244" s="20"/>
       <c r="Q244" s="21"/>
     </row>
-    <row r="245" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="20"/>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -29790,7 +29794,7 @@
       <c r="P245" s="20"/>
       <c r="Q245" s="21"/>
     </row>
-    <row r="246" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="20"/>
       <c r="B246" s="20"/>
       <c r="C246" s="20"/>
@@ -29809,7 +29813,7 @@
       <c r="P246" s="20"/>
       <c r="Q246" s="21"/>
     </row>
-    <row r="247" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="20"/>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -29828,7 +29832,7 @@
       <c r="P247" s="20"/>
       <c r="Q247" s="21"/>
     </row>
-    <row r="248" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="20"/>
       <c r="B248" s="20"/>
       <c r="C248" s="20"/>
@@ -29847,7 +29851,7 @@
       <c r="P248" s="20"/>
       <c r="Q248" s="21"/>
     </row>
-    <row r="249" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="20"/>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -29866,7 +29870,7 @@
       <c r="P249" s="20"/>
       <c r="Q249" s="21"/>
     </row>
-    <row r="250" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="20"/>
       <c r="B250" s="20"/>
       <c r="C250" s="20"/>
@@ -29885,7 +29889,7 @@
       <c r="P250" s="20"/>
       <c r="Q250" s="21"/>
     </row>
-    <row r="251" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="20"/>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -29904,7 +29908,7 @@
       <c r="P251" s="20"/>
       <c r="Q251" s="21"/>
     </row>
-    <row r="252" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="20"/>
       <c r="B252" s="20"/>
       <c r="C252" s="20"/>
@@ -29923,7 +29927,7 @@
       <c r="P252" s="20"/>
       <c r="Q252" s="21"/>
     </row>
-    <row r="253" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="20"/>
       <c r="B253" s="20"/>
       <c r="C253" s="20"/>
@@ -29942,7 +29946,7 @@
       <c r="P253" s="20"/>
       <c r="Q253" s="21"/>
     </row>
-    <row r="254" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="20"/>
       <c r="B254" s="20"/>
       <c r="C254" s="20"/>
@@ -29961,7 +29965,7 @@
       <c r="P254" s="20"/>
       <c r="Q254" s="21"/>
     </row>
-    <row r="255" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="20"/>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -29980,7 +29984,7 @@
       <c r="P255" s="20"/>
       <c r="Q255" s="21"/>
     </row>
-    <row r="256" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="20"/>
       <c r="B256" s="20"/>
       <c r="C256" s="20"/>
@@ -29999,7 +30003,7 @@
       <c r="P256" s="20"/>
       <c r="Q256" s="21"/>
     </row>
-    <row r="257" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="20"/>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -30018,7 +30022,7 @@
       <c r="P257" s="20"/>
       <c r="Q257" s="21"/>
     </row>
-    <row r="258" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="20"/>
       <c r="B258" s="20"/>
       <c r="C258" s="20"/>
@@ -30037,7 +30041,7 @@
       <c r="P258" s="20"/>
       <c r="Q258" s="21"/>
     </row>
-    <row r="259" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="20"/>
       <c r="B259" s="20"/>
       <c r="C259" s="20"/>
@@ -30056,7 +30060,7 @@
       <c r="P259" s="20"/>
       <c r="Q259" s="21"/>
     </row>
-    <row r="260" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="20"/>
       <c r="B260" s="20"/>
       <c r="C260" s="20"/>
@@ -30075,7 +30079,7 @@
       <c r="P260" s="20"/>
       <c r="Q260" s="21"/>
     </row>
-    <row r="261" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="20"/>
       <c r="B261" s="20"/>
       <c r="C261" s="20"/>
@@ -30094,7 +30098,7 @@
       <c r="P261" s="20"/>
       <c r="Q261" s="21"/>
     </row>
-    <row r="262" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="20"/>
       <c r="B262" s="20"/>
       <c r="C262" s="20"/>
@@ -30113,7 +30117,7 @@
       <c r="P262" s="20"/>
       <c r="Q262" s="21"/>
     </row>
-    <row r="263" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="20"/>
       <c r="B263" s="20"/>
       <c r="C263" s="20"/>
@@ -30132,7 +30136,7 @@
       <c r="P263" s="20"/>
       <c r="Q263" s="21"/>
     </row>
-    <row r="264" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="20"/>
       <c r="B264" s="20"/>
       <c r="C264" s="20"/>
@@ -30151,7 +30155,7 @@
       <c r="P264" s="20"/>
       <c r="Q264" s="21"/>
     </row>
-    <row r="265" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="20"/>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -30170,7 +30174,7 @@
       <c r="P265" s="20"/>
       <c r="Q265" s="21"/>
     </row>
-    <row r="266" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="20"/>
       <c r="B266" s="20"/>
       <c r="C266" s="20"/>
@@ -30189,7 +30193,7 @@
       <c r="P266" s="20"/>
       <c r="Q266" s="21"/>
     </row>
-    <row r="267" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="20"/>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -30208,7 +30212,7 @@
       <c r="P267" s="20"/>
       <c r="Q267" s="21"/>
     </row>
-    <row r="268" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="20"/>
       <c r="B268" s="20"/>
       <c r="C268" s="20"/>
@@ -30227,7 +30231,7 @@
       <c r="P268" s="20"/>
       <c r="Q268" s="21"/>
     </row>
-    <row r="269" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -30246,7 +30250,7 @@
       <c r="P269" s="20"/>
       <c r="Q269" s="21"/>
     </row>
-    <row r="270" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="20"/>
       <c r="B270" s="20"/>
       <c r="C270" s="20"/>
@@ -30265,7 +30269,7 @@
       <c r="P270" s="20"/>
       <c r="Q270" s="21"/>
     </row>
-    <row r="271" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="20"/>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -30284,7 +30288,7 @@
       <c r="P271" s="20"/>
       <c r="Q271" s="21"/>
     </row>
-    <row r="272" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="20"/>
       <c r="B272" s="20"/>
       <c r="C272" s="20"/>
@@ -30303,7 +30307,7 @@
       <c r="P272" s="20"/>
       <c r="Q272" s="21"/>
     </row>
-    <row r="273" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="20"/>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -30322,7 +30326,7 @@
       <c r="P273" s="20"/>
       <c r="Q273" s="21"/>
     </row>
-    <row r="274" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="20"/>
       <c r="B274" s="20"/>
       <c r="C274" s="20"/>
@@ -30341,7 +30345,7 @@
       <c r="P274" s="20"/>
       <c r="Q274" s="21"/>
     </row>
-    <row r="275" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="20"/>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -30360,7 +30364,7 @@
       <c r="P275" s="20"/>
       <c r="Q275" s="21"/>
     </row>
-    <row r="276" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="20"/>
       <c r="B276" s="20"/>
       <c r="C276" s="20"/>
@@ -30379,7 +30383,7 @@
       <c r="P276" s="20"/>
       <c r="Q276" s="21"/>
     </row>
-    <row r="277" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="20"/>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -30398,7 +30402,7 @@
       <c r="P277" s="20"/>
       <c r="Q277" s="21"/>
     </row>
-    <row r="278" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="20"/>
       <c r="B278" s="20"/>
       <c r="C278" s="20"/>
@@ -30417,7 +30421,7 @@
       <c r="P278" s="20"/>
       <c r="Q278" s="21"/>
     </row>
-    <row r="279" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="20"/>
       <c r="B279" s="20"/>
       <c r="C279" s="20"/>
@@ -30436,7 +30440,7 @@
       <c r="P279" s="20"/>
       <c r="Q279" s="21"/>
     </row>
-    <row r="280" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="20"/>
       <c r="B280" s="20"/>
       <c r="C280" s="20"/>
@@ -30455,7 +30459,7 @@
       <c r="P280" s="20"/>
       <c r="Q280" s="21"/>
     </row>
-    <row r="281" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="20"/>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -30474,7 +30478,7 @@
       <c r="P281" s="20"/>
       <c r="Q281" s="21"/>
     </row>
-    <row r="282" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="20"/>
       <c r="B282" s="20"/>
       <c r="C282" s="20"/>
@@ -30493,7 +30497,7 @@
       <c r="P282" s="20"/>
       <c r="Q282" s="21"/>
     </row>
-    <row r="283" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="20"/>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -30512,7 +30516,7 @@
       <c r="P283" s="20"/>
       <c r="Q283" s="21"/>
     </row>
-    <row r="284" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="20"/>
       <c r="B284" s="20"/>
       <c r="C284" s="20"/>
@@ -30531,7 +30535,7 @@
       <c r="P284" s="20"/>
       <c r="Q284" s="21"/>
     </row>
-    <row r="285" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="20"/>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -30550,7 +30554,7 @@
       <c r="P285" s="20"/>
       <c r="Q285" s="21"/>
     </row>
-    <row r="286" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="20"/>
       <c r="B286" s="20"/>
       <c r="C286" s="20"/>
@@ -30569,7 +30573,7 @@
       <c r="P286" s="20"/>
       <c r="Q286" s="21"/>
     </row>
-    <row r="287" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="20"/>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -30588,7 +30592,7 @@
       <c r="P287" s="20"/>
       <c r="Q287" s="21"/>
     </row>
-    <row r="288" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="20"/>
       <c r="B288" s="20"/>
       <c r="C288" s="20"/>
@@ -30607,7 +30611,7 @@
       <c r="P288" s="20"/>
       <c r="Q288" s="21"/>
     </row>
-    <row r="289" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="20"/>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -30626,7 +30630,7 @@
       <c r="P289" s="20"/>
       <c r="Q289" s="21"/>
     </row>
-    <row r="290" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="20"/>
       <c r="B290" s="20"/>
       <c r="C290" s="20"/>
@@ -30645,7 +30649,7 @@
       <c r="P290" s="20"/>
       <c r="Q290" s="21"/>
     </row>
-    <row r="291" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="20"/>
       <c r="B291" s="20"/>
       <c r="C291" s="20"/>
@@ -30664,7 +30668,7 @@
       <c r="P291" s="20"/>
       <c r="Q291" s="21"/>
     </row>
-    <row r="292" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="20"/>
       <c r="B292" s="20"/>
       <c r="C292" s="20"/>
@@ -30683,7 +30687,7 @@
       <c r="P292" s="20"/>
       <c r="Q292" s="21"/>
     </row>
-    <row r="293" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="20"/>
       <c r="B293" s="20"/>
       <c r="C293" s="20"/>
@@ -30702,7 +30706,7 @@
       <c r="P293" s="20"/>
       <c r="Q293" s="21"/>
     </row>
-    <row r="294" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="20"/>
       <c r="B294" s="20"/>
       <c r="C294" s="20"/>
@@ -30721,7 +30725,7 @@
       <c r="P294" s="20"/>
       <c r="Q294" s="21"/>
     </row>
-    <row r="295" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="20"/>
       <c r="B295" s="20"/>
       <c r="C295" s="20"/>
@@ -30740,7 +30744,7 @@
       <c r="P295" s="20"/>
       <c r="Q295" s="21"/>
     </row>
-    <row r="296" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="20"/>
       <c r="B296" s="20"/>
       <c r="C296" s="20"/>
@@ -30759,7 +30763,7 @@
       <c r="P296" s="20"/>
       <c r="Q296" s="21"/>
     </row>
-    <row r="297" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="20"/>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -30778,7 +30782,7 @@
       <c r="P297" s="20"/>
       <c r="Q297" s="21"/>
     </row>
-    <row r="298" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="20"/>
       <c r="B298" s="20"/>
       <c r="C298" s="20"/>
@@ -30797,7 +30801,7 @@
       <c r="P298" s="20"/>
       <c r="Q298" s="21"/>
     </row>
-    <row r="299" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="20"/>
       <c r="B299" s="20"/>
       <c r="C299" s="20"/>
@@ -30816,7 +30820,7 @@
       <c r="P299" s="20"/>
       <c r="Q299" s="21"/>
     </row>
-    <row r="300" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="20"/>
       <c r="B300" s="20"/>
       <c r="C300" s="20"/>
@@ -30835,7 +30839,7 @@
       <c r="P300" s="20"/>
       <c r="Q300" s="21"/>
     </row>
-    <row r="301" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="20"/>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -30854,7 +30858,7 @@
       <c r="P301" s="20"/>
       <c r="Q301" s="21"/>
     </row>
-    <row r="302" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="20"/>
       <c r="B302" s="20"/>
       <c r="C302" s="20"/>
@@ -30873,7 +30877,7 @@
       <c r="P302" s="20"/>
       <c r="Q302" s="21"/>
     </row>
-    <row r="303" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="20"/>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -30892,7 +30896,7 @@
       <c r="P303" s="20"/>
       <c r="Q303" s="21"/>
     </row>
-    <row r="304" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="20"/>
       <c r="B304" s="20"/>
       <c r="C304" s="20"/>
@@ -30911,7 +30915,7 @@
       <c r="P304" s="20"/>
       <c r="Q304" s="21"/>
     </row>
-    <row r="305" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="20"/>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -30930,7 +30934,7 @@
       <c r="P305" s="20"/>
       <c r="Q305" s="21"/>
     </row>
-    <row r="306" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="20"/>
       <c r="B306" s="20"/>
       <c r="C306" s="20"/>
@@ -30949,7 +30953,7 @@
       <c r="P306" s="20"/>
       <c r="Q306" s="21"/>
     </row>
-    <row r="307" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="20"/>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -30968,7 +30972,7 @@
       <c r="P307" s="20"/>
       <c r="Q307" s="21"/>
     </row>
-    <row r="308" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="20"/>
       <c r="B308" s="20"/>
       <c r="C308" s="20"/>
@@ -30987,7 +30991,7 @@
       <c r="P308" s="20"/>
       <c r="Q308" s="21"/>
     </row>
-    <row r="309" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="20"/>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -31006,7 +31010,7 @@
       <c r="P309" s="20"/>
       <c r="Q309" s="21"/>
     </row>
-    <row r="310" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="20"/>
       <c r="B310" s="20"/>
       <c r="C310" s="20"/>
@@ -31025,7 +31029,7 @@
       <c r="P310" s="20"/>
       <c r="Q310" s="21"/>
     </row>
-    <row r="311" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="20"/>
       <c r="B311" s="20"/>
       <c r="C311" s="20"/>
@@ -31044,7 +31048,7 @@
       <c r="P311" s="20"/>
       <c r="Q311" s="21"/>
     </row>
-    <row r="312" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="20"/>
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
@@ -31063,7 +31067,7 @@
       <c r="P312" s="20"/>
       <c r="Q312" s="21"/>
     </row>
-    <row r="313" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="20"/>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -31082,7 +31086,7 @@
       <c r="P313" s="20"/>
       <c r="Q313" s="21"/>
     </row>
-    <row r="314" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="20"/>
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
@@ -31101,7 +31105,7 @@
       <c r="P314" s="20"/>
       <c r="Q314" s="21"/>
     </row>
-    <row r="315" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="20"/>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -31120,7 +31124,7 @@
       <c r="P315" s="20"/>
       <c r="Q315" s="21"/>
     </row>
-    <row r="316" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="20"/>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>
@@ -31139,7 +31143,7 @@
       <c r="P316" s="20"/>
       <c r="Q316" s="21"/>
     </row>
-    <row r="317" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="20"/>
       <c r="B317" s="20"/>
       <c r="C317" s="20"/>
@@ -31158,7 +31162,7 @@
       <c r="P317" s="20"/>
       <c r="Q317" s="21"/>
     </row>
-    <row r="318" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="20"/>
       <c r="B318" s="20"/>
       <c r="C318" s="20"/>
@@ -31177,7 +31181,7 @@
       <c r="P318" s="20"/>
       <c r="Q318" s="21"/>
     </row>
-    <row r="319" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="20"/>
       <c r="B319" s="20"/>
       <c r="C319" s="20"/>
@@ -31196,7 +31200,7 @@
       <c r="P319" s="20"/>
       <c r="Q319" s="21"/>
     </row>
-    <row r="320" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="20"/>
       <c r="B320" s="20"/>
       <c r="C320" s="20"/>
@@ -31215,7 +31219,7 @@
       <c r="P320" s="20"/>
       <c r="Q320" s="21"/>
     </row>
-    <row r="321" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="20"/>
       <c r="B321" s="20"/>
       <c r="C321" s="20"/>
@@ -31234,7 +31238,7 @@
       <c r="P321" s="20"/>
       <c r="Q321" s="21"/>
     </row>
-    <row r="322" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="20"/>
       <c r="B322" s="20"/>
       <c r="C322" s="20"/>
@@ -31253,7 +31257,7 @@
       <c r="P322" s="20"/>
       <c r="Q322" s="21"/>
     </row>
-    <row r="323" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="20"/>
       <c r="B323" s="20"/>
       <c r="C323" s="20"/>
@@ -31272,7 +31276,7 @@
       <c r="P323" s="20"/>
       <c r="Q323" s="21"/>
     </row>
-    <row r="324" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="20"/>
       <c r="B324" s="20"/>
       <c r="C324" s="20"/>
@@ -31291,7 +31295,7 @@
       <c r="P324" s="20"/>
       <c r="Q324" s="21"/>
     </row>
-    <row r="325" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="20"/>
       <c r="B325" s="20"/>
       <c r="C325" s="20"/>
@@ -31310,7 +31314,7 @@
       <c r="P325" s="20"/>
       <c r="Q325" s="21"/>
     </row>
-    <row r="326" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="20"/>
       <c r="B326" s="20"/>
       <c r="C326" s="20"/>
@@ -31329,7 +31333,7 @@
       <c r="P326" s="20"/>
       <c r="Q326" s="21"/>
     </row>
-    <row r="327" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="20"/>
       <c r="B327" s="20"/>
       <c r="C327" s="20"/>
@@ -31348,7 +31352,7 @@
       <c r="P327" s="20"/>
       <c r="Q327" s="21"/>
     </row>
-    <row r="328" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="20"/>
       <c r="B328" s="20"/>
       <c r="C328" s="20"/>
@@ -31367,7 +31371,7 @@
       <c r="P328" s="20"/>
       <c r="Q328" s="21"/>
     </row>
-    <row r="329" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="20"/>
       <c r="B329" s="20"/>
       <c r="C329" s="20"/>
@@ -31386,7 +31390,7 @@
       <c r="P329" s="20"/>
       <c r="Q329" s="21"/>
     </row>
-    <row r="330" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="20"/>
       <c r="B330" s="20"/>
       <c r="C330" s="20"/>
@@ -31405,7 +31409,7 @@
       <c r="P330" s="20"/>
       <c r="Q330" s="21"/>
     </row>
-    <row r="331" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="20"/>
       <c r="B331" s="20"/>
       <c r="C331" s="20"/>
@@ -31424,7 +31428,7 @@
       <c r="P331" s="20"/>
       <c r="Q331" s="21"/>
     </row>
-    <row r="332" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="20"/>
       <c r="B332" s="20"/>
       <c r="C332" s="20"/>
@@ -31443,7 +31447,7 @@
       <c r="P332" s="20"/>
       <c r="Q332" s="21"/>
     </row>
-    <row r="333" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="20"/>
       <c r="B333" s="20"/>
       <c r="C333" s="20"/>
@@ -31462,7 +31466,7 @@
       <c r="P333" s="20"/>
       <c r="Q333" s="21"/>
     </row>
-    <row r="334" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="20"/>
       <c r="B334" s="20"/>
       <c r="C334" s="20"/>
@@ -31481,7 +31485,7 @@
       <c r="P334" s="20"/>
       <c r="Q334" s="21"/>
     </row>
-    <row r="335" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="20"/>
       <c r="B335" s="20"/>
       <c r="C335" s="20"/>
@@ -31500,7 +31504,7 @@
       <c r="P335" s="20"/>
       <c r="Q335" s="21"/>
     </row>
-    <row r="336" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="20"/>
       <c r="B336" s="20"/>
       <c r="C336" s="20"/>
@@ -31519,7 +31523,7 @@
       <c r="P336" s="20"/>
       <c r="Q336" s="21"/>
     </row>
-    <row r="337" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="20"/>
       <c r="B337" s="20"/>
       <c r="C337" s="20"/>
@@ -31538,7 +31542,7 @@
       <c r="P337" s="20"/>
       <c r="Q337" s="21"/>
     </row>
-    <row r="338" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="20"/>
       <c r="B338" s="20"/>
       <c r="C338" s="20"/>
@@ -31557,7 +31561,7 @@
       <c r="P338" s="20"/>
       <c r="Q338" s="21"/>
     </row>
-    <row r="339" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="20"/>
       <c r="B339" s="20"/>
       <c r="C339" s="20"/>
@@ -31576,7 +31580,7 @@
       <c r="P339" s="20"/>
       <c r="Q339" s="21"/>
     </row>
-    <row r="340" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="20"/>
       <c r="B340" s="20"/>
       <c r="C340" s="20"/>
@@ -31595,7 +31599,7 @@
       <c r="P340" s="20"/>
       <c r="Q340" s="21"/>
     </row>
-    <row r="341" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="20"/>
       <c r="B341" s="20"/>
       <c r="C341" s="20"/>
@@ -31614,7 +31618,7 @@
       <c r="P341" s="20"/>
       <c r="Q341" s="21"/>
     </row>
-    <row r="342" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="20"/>
       <c r="B342" s="20"/>
       <c r="C342" s="20"/>
@@ -31633,7 +31637,7 @@
       <c r="P342" s="20"/>
       <c r="Q342" s="21"/>
     </row>
-    <row r="343" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="20"/>
       <c r="B343" s="20"/>
       <c r="C343" s="20"/>
@@ -31652,7 +31656,7 @@
       <c r="P343" s="20"/>
       <c r="Q343" s="21"/>
     </row>
-    <row r="344" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="20"/>
       <c r="B344" s="20"/>
       <c r="C344" s="20"/>
@@ -31671,7 +31675,7 @@
       <c r="P344" s="20"/>
       <c r="Q344" s="21"/>
     </row>
-    <row r="345" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="20"/>
       <c r="B345" s="20"/>
       <c r="C345" s="20"/>
@@ -31690,7 +31694,7 @@
       <c r="P345" s="20"/>
       <c r="Q345" s="21"/>
     </row>
-    <row r="346" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="20"/>
       <c r="B346" s="20"/>
       <c r="C346" s="20"/>
@@ -31709,7 +31713,7 @@
       <c r="P346" s="20"/>
       <c r="Q346" s="21"/>
     </row>
-    <row r="347" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="20"/>
       <c r="B347" s="20"/>
       <c r="C347" s="20"/>
@@ -31728,7 +31732,7 @@
       <c r="P347" s="20"/>
       <c r="Q347" s="21"/>
     </row>
-    <row r="348" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="20"/>
       <c r="B348" s="20"/>
       <c r="C348" s="20"/>
@@ -31747,7 +31751,7 @@
       <c r="P348" s="20"/>
       <c r="Q348" s="21"/>
     </row>
-    <row r="349" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="20"/>
       <c r="B349" s="20"/>
       <c r="C349" s="20"/>
@@ -31766,7 +31770,7 @@
       <c r="P349" s="20"/>
       <c r="Q349" s="21"/>
     </row>
-    <row r="350" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="20"/>
       <c r="B350" s="20"/>
       <c r="C350" s="20"/>
@@ -31785,7 +31789,7 @@
       <c r="P350" s="20"/>
       <c r="Q350" s="21"/>
     </row>
-    <row r="351" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="20"/>
       <c r="B351" s="20"/>
       <c r="C351" s="20"/>
@@ -31804,7 +31808,7 @@
       <c r="P351" s="20"/>
       <c r="Q351" s="21"/>
     </row>
-    <row r="352" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="20"/>
       <c r="B352" s="20"/>
       <c r="C352" s="20"/>
@@ -31823,7 +31827,7 @@
       <c r="P352" s="20"/>
       <c r="Q352" s="21"/>
     </row>
-    <row r="353" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="20"/>
       <c r="B353" s="20"/>
       <c r="C353" s="20"/>
@@ -31842,7 +31846,7 @@
       <c r="P353" s="20"/>
       <c r="Q353" s="21"/>
     </row>
-    <row r="354" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="20"/>
       <c r="B354" s="20"/>
       <c r="C354" s="20"/>
@@ -31861,7 +31865,7 @@
       <c r="P354" s="20"/>
       <c r="Q354" s="21"/>
     </row>
-    <row r="355" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="20"/>
       <c r="B355" s="20"/>
       <c r="C355" s="20"/>
@@ -31880,7 +31884,7 @@
       <c r="P355" s="20"/>
       <c r="Q355" s="21"/>
     </row>
-    <row r="356" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="20"/>
       <c r="B356" s="20"/>
       <c r="C356" s="20"/>
@@ -31899,7 +31903,7 @@
       <c r="P356" s="20"/>
       <c r="Q356" s="21"/>
     </row>
-    <row r="357" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="20"/>
       <c r="B357" s="20"/>
       <c r="C357" s="20"/>
@@ -31918,7 +31922,7 @@
       <c r="P357" s="20"/>
       <c r="Q357" s="21"/>
     </row>
-    <row r="358" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="20"/>
       <c r="B358" s="20"/>
       <c r="C358" s="20"/>
@@ -31937,7 +31941,7 @@
       <c r="P358" s="20"/>
       <c r="Q358" s="21"/>
     </row>
-    <row r="359" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="20"/>
       <c r="B359" s="20"/>
       <c r="C359" s="20"/>
@@ -31956,7 +31960,7 @@
       <c r="P359" s="20"/>
       <c r="Q359" s="21"/>
     </row>
-    <row r="360" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="20"/>
       <c r="B360" s="20"/>
       <c r="C360" s="20"/>
@@ -31975,7 +31979,7 @@
       <c r="P360" s="20"/>
       <c r="Q360" s="21"/>
     </row>
-    <row r="361" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="20"/>
       <c r="B361" s="20"/>
       <c r="C361" s="20"/>
@@ -31994,7 +31998,7 @@
       <c r="P361" s="20"/>
       <c r="Q361" s="21"/>
     </row>
-    <row r="362" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="20"/>
       <c r="B362" s="20"/>
       <c r="C362" s="20"/>
@@ -32013,7 +32017,7 @@
       <c r="P362" s="20"/>
       <c r="Q362" s="21"/>
     </row>
-    <row r="363" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="20"/>
       <c r="B363" s="20"/>
       <c r="C363" s="20"/>
@@ -32032,7 +32036,7 @@
       <c r="P363" s="20"/>
       <c r="Q363" s="21"/>
     </row>
-    <row r="364" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="20"/>
       <c r="B364" s="20"/>
       <c r="C364" s="20"/>
@@ -32051,7 +32055,7 @@
       <c r="P364" s="20"/>
       <c r="Q364" s="21"/>
     </row>
-    <row r="365" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="20"/>
       <c r="B365" s="20"/>
       <c r="C365" s="20"/>
@@ -32070,7 +32074,7 @@
       <c r="P365" s="20"/>
       <c r="Q365" s="21"/>
     </row>
-    <row r="366" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="20"/>
       <c r="B366" s="20"/>
       <c r="C366" s="20"/>
@@ -32089,7 +32093,7 @@
       <c r="P366" s="20"/>
       <c r="Q366" s="21"/>
     </row>
-    <row r="367" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="20"/>
       <c r="B367" s="20"/>
       <c r="C367" s="20"/>
@@ -32108,7 +32112,7 @@
       <c r="P367" s="20"/>
       <c r="Q367" s="21"/>
     </row>
-    <row r="368" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="20"/>
       <c r="B368" s="20"/>
       <c r="C368" s="20"/>
@@ -32127,7 +32131,7 @@
       <c r="P368" s="20"/>
       <c r="Q368" s="21"/>
     </row>
-    <row r="369" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="20"/>
       <c r="B369" s="20"/>
       <c r="C369" s="20"/>
@@ -32146,7 +32150,7 @@
       <c r="P369" s="20"/>
       <c r="Q369" s="21"/>
     </row>
-    <row r="370" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="20"/>
       <c r="B370" s="20"/>
       <c r="C370" s="20"/>
@@ -32165,7 +32169,7 @@
       <c r="P370" s="20"/>
       <c r="Q370" s="21"/>
     </row>
-    <row r="371" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="20"/>
       <c r="B371" s="20"/>
       <c r="C371" s="20"/>
@@ -32184,7 +32188,7 @@
       <c r="P371" s="20"/>
       <c r="Q371" s="21"/>
     </row>
-    <row r="372" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="20"/>
       <c r="B372" s="20"/>
       <c r="C372" s="20"/>
@@ -32203,7 +32207,7 @@
       <c r="P372" s="20"/>
       <c r="Q372" s="21"/>
     </row>
-    <row r="373" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="20"/>
       <c r="B373" s="20"/>
       <c r="C373" s="20"/>
@@ -32222,7 +32226,7 @@
       <c r="P373" s="20"/>
       <c r="Q373" s="21"/>
     </row>
-    <row r="374" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="20"/>
       <c r="B374" s="20"/>
       <c r="C374" s="20"/>
@@ -32241,7 +32245,7 @@
       <c r="P374" s="20"/>
       <c r="Q374" s="21"/>
     </row>
-    <row r="375" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="20"/>
       <c r="B375" s="20"/>
       <c r="C375" s="20"/>
@@ -32260,7 +32264,7 @@
       <c r="P375" s="20"/>
       <c r="Q375" s="21"/>
     </row>
-    <row r="376" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="20"/>
       <c r="B376" s="20"/>
       <c r="C376" s="20"/>
@@ -32279,7 +32283,7 @@
       <c r="P376" s="20"/>
       <c r="Q376" s="21"/>
     </row>
-    <row r="377" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="20"/>
       <c r="B377" s="20"/>
       <c r="C377" s="20"/>
@@ -32298,7 +32302,7 @@
       <c r="P377" s="20"/>
       <c r="Q377" s="21"/>
     </row>
-    <row r="378" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="20"/>
       <c r="B378" s="20"/>
       <c r="C378" s="20"/>
@@ -32317,7 +32321,7 @@
       <c r="P378" s="20"/>
       <c r="Q378" s="21"/>
     </row>
-    <row r="379" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="20"/>
       <c r="B379" s="20"/>
       <c r="C379" s="20"/>
@@ -32336,7 +32340,7 @@
       <c r="P379" s="20"/>
       <c r="Q379" s="21"/>
     </row>
-    <row r="380" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="20"/>
       <c r="B380" s="20"/>
       <c r="C380" s="20"/>
@@ -32355,7 +32359,7 @@
       <c r="P380" s="20"/>
       <c r="Q380" s="21"/>
     </row>
-    <row r="381" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="20"/>
       <c r="B381" s="20"/>
       <c r="C381" s="20"/>
@@ -32374,7 +32378,7 @@
       <c r="P381" s="20"/>
       <c r="Q381" s="21"/>
     </row>
-    <row r="382" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="20"/>
       <c r="B382" s="20"/>
       <c r="C382" s="20"/>
@@ -32393,7 +32397,7 @@
       <c r="P382" s="20"/>
       <c r="Q382" s="21"/>
     </row>
-    <row r="383" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="20"/>
       <c r="B383" s="20"/>
       <c r="C383" s="20"/>
@@ -32412,7 +32416,7 @@
       <c r="P383" s="20"/>
       <c r="Q383" s="21"/>
     </row>
-    <row r="384" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="20"/>
       <c r="B384" s="20"/>
       <c r="C384" s="20"/>
@@ -32431,7 +32435,7 @@
       <c r="P384" s="20"/>
       <c r="Q384" s="21"/>
     </row>
-    <row r="385" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="20"/>
       <c r="B385" s="20"/>
       <c r="C385" s="20"/>
@@ -32450,7 +32454,7 @@
       <c r="P385" s="20"/>
       <c r="Q385" s="21"/>
     </row>
-    <row r="386" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="20"/>
       <c r="B386" s="20"/>
       <c r="C386" s="20"/>
@@ -32469,7 +32473,7 @@
       <c r="P386" s="20"/>
       <c r="Q386" s="21"/>
     </row>
-    <row r="387" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="20"/>
       <c r="B387" s="20"/>
       <c r="C387" s="20"/>
@@ -32488,7 +32492,7 @@
       <c r="P387" s="20"/>
       <c r="Q387" s="21"/>
     </row>
-    <row r="388" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="20"/>
       <c r="B388" s="20"/>
       <c r="C388" s="20"/>
@@ -32507,7 +32511,7 @@
       <c r="P388" s="20"/>
       <c r="Q388" s="21"/>
     </row>
-    <row r="389" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="20"/>
       <c r="B389" s="20"/>
       <c r="C389" s="20"/>
@@ -32526,7 +32530,7 @@
       <c r="P389" s="20"/>
       <c r="Q389" s="21"/>
     </row>
-    <row r="390" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="20"/>
       <c r="B390" s="20"/>
       <c r="C390" s="20"/>
@@ -32545,7 +32549,7 @@
       <c r="P390" s="20"/>
       <c r="Q390" s="21"/>
     </row>
-    <row r="391" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="20"/>
       <c r="B391" s="20"/>
       <c r="C391" s="20"/>
@@ -32564,7 +32568,7 @@
       <c r="P391" s="20"/>
       <c r="Q391" s="21"/>
     </row>
-    <row r="392" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="20"/>
       <c r="B392" s="20"/>
       <c r="C392" s="20"/>
@@ -32583,7 +32587,7 @@
       <c r="P392" s="20"/>
       <c r="Q392" s="21"/>
     </row>
-    <row r="393" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="20"/>
       <c r="B393" s="20"/>
       <c r="C393" s="20"/>
@@ -32602,7 +32606,7 @@
       <c r="P393" s="20"/>
       <c r="Q393" s="21"/>
     </row>
-    <row r="394" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="20"/>
       <c r="B394" s="20"/>
       <c r="C394" s="20"/>
@@ -32621,7 +32625,7 @@
       <c r="P394" s="20"/>
       <c r="Q394" s="21"/>
     </row>
-    <row r="395" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="20"/>
       <c r="B395" s="20"/>
       <c r="C395" s="20"/>
@@ -32640,7 +32644,7 @@
       <c r="P395" s="20"/>
       <c r="Q395" s="21"/>
     </row>
-    <row r="396" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="20"/>
       <c r="B396" s="20"/>
       <c r="C396" s="20"/>
@@ -32659,7 +32663,7 @@
       <c r="P396" s="20"/>
       <c r="Q396" s="21"/>
     </row>
-    <row r="397" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="20"/>
       <c r="B397" s="20"/>
       <c r="C397" s="20"/>
@@ -32678,7 +32682,7 @@
       <c r="P397" s="20"/>
       <c r="Q397" s="21"/>
     </row>
-    <row r="398" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="20"/>
       <c r="B398" s="20"/>
       <c r="C398" s="20"/>
@@ -32697,7 +32701,7 @@
       <c r="P398" s="20"/>
       <c r="Q398" s="21"/>
     </row>
-    <row r="399" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="20"/>
       <c r="B399" s="20"/>
       <c r="C399" s="20"/>
@@ -32716,7 +32720,7 @@
       <c r="P399" s="20"/>
       <c r="Q399" s="21"/>
     </row>
-    <row r="400" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="20"/>
       <c r="B400" s="20"/>
       <c r="C400" s="20"/>
@@ -32735,7 +32739,7 @@
       <c r="P400" s="20"/>
       <c r="Q400" s="21"/>
     </row>
-    <row r="401" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="20"/>
       <c r="B401" s="20"/>
       <c r="C401" s="20"/>
@@ -32754,7 +32758,7 @@
       <c r="P401" s="20"/>
       <c r="Q401" s="21"/>
     </row>
-    <row r="402" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="20"/>
       <c r="B402" s="20"/>
       <c r="C402" s="20"/>
@@ -32773,7 +32777,7 @@
       <c r="P402" s="20"/>
       <c r="Q402" s="21"/>
     </row>
-    <row r="403" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="20"/>
       <c r="B403" s="20"/>
       <c r="C403" s="20"/>
@@ -32792,7 +32796,7 @@
       <c r="P403" s="20"/>
       <c r="Q403" s="21"/>
     </row>
-    <row r="404" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="20"/>
       <c r="B404" s="20"/>
       <c r="C404" s="20"/>
@@ -32811,7 +32815,7 @@
       <c r="P404" s="20"/>
       <c r="Q404" s="21"/>
     </row>
-    <row r="405" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="20"/>
       <c r="B405" s="20"/>
       <c r="C405" s="20"/>
@@ -32830,7 +32834,7 @@
       <c r="P405" s="20"/>
       <c r="Q405" s="21"/>
     </row>
-    <row r="406" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="20"/>
       <c r="B406" s="20"/>
       <c r="C406" s="20"/>
@@ -32849,7 +32853,7 @@
       <c r="P406" s="20"/>
       <c r="Q406" s="21"/>
     </row>
-    <row r="407" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="20"/>
       <c r="B407" s="20"/>
       <c r="C407" s="20"/>
@@ -32868,7 +32872,7 @@
       <c r="P407" s="20"/>
       <c r="Q407" s="21"/>
     </row>
-    <row r="408" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="20"/>
       <c r="B408" s="20"/>
       <c r="C408" s="20"/>
@@ -32887,7 +32891,7 @@
       <c r="P408" s="20"/>
       <c r="Q408" s="21"/>
     </row>
-    <row r="409" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="20"/>
       <c r="B409" s="20"/>
       <c r="C409" s="20"/>
@@ -32906,7 +32910,7 @@
       <c r="P409" s="20"/>
       <c r="Q409" s="21"/>
     </row>
-    <row r="410" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="20"/>
       <c r="B410" s="20"/>
       <c r="C410" s="20"/>
@@ -32925,7 +32929,7 @@
       <c r="P410" s="20"/>
       <c r="Q410" s="21"/>
     </row>
-    <row r="411" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="20"/>
       <c r="B411" s="20"/>
       <c r="C411" s="20"/>
@@ -32944,7 +32948,7 @@
       <c r="P411" s="20"/>
       <c r="Q411" s="21"/>
     </row>
-    <row r="412" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="20"/>
       <c r="B412" s="20"/>
       <c r="C412" s="20"/>
@@ -32963,7 +32967,7 @@
       <c r="P412" s="20"/>
       <c r="Q412" s="21"/>
     </row>
-    <row r="413" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="20"/>
       <c r="B413" s="20"/>
       <c r="C413" s="20"/>
@@ -32982,7 +32986,7 @@
       <c r="P413" s="20"/>
       <c r="Q413" s="21"/>
     </row>
-    <row r="414" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="20"/>
       <c r="B414" s="20"/>
       <c r="C414" s="20"/>
@@ -33001,7 +33005,7 @@
       <c r="P414" s="20"/>
       <c r="Q414" s="21"/>
     </row>
-    <row r="415" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="20"/>
       <c r="B415" s="20"/>
       <c r="C415" s="20"/>
@@ -33020,7 +33024,7 @@
       <c r="P415" s="20"/>
       <c r="Q415" s="21"/>
     </row>
-    <row r="416" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="20"/>
       <c r="B416" s="20"/>
       <c r="C416" s="20"/>
@@ -33039,7 +33043,7 @@
       <c r="P416" s="20"/>
       <c r="Q416" s="21"/>
     </row>
-    <row r="417" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="20"/>
       <c r="B417" s="20"/>
       <c r="C417" s="20"/>
@@ -33058,7 +33062,7 @@
       <c r="P417" s="20"/>
       <c r="Q417" s="21"/>
     </row>
-    <row r="418" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="20"/>
       <c r="B418" s="20"/>
       <c r="C418" s="20"/>
@@ -33077,7 +33081,7 @@
       <c r="P418" s="20"/>
       <c r="Q418" s="21"/>
     </row>
-    <row r="419" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="20"/>
       <c r="B419" s="20"/>
       <c r="C419" s="20"/>
@@ -33096,7 +33100,7 @@
       <c r="P419" s="20"/>
       <c r="Q419" s="21"/>
     </row>
-    <row r="420" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="20"/>
       <c r="B420" s="20"/>
       <c r="C420" s="20"/>
@@ -33115,7 +33119,7 @@
       <c r="P420" s="20"/>
       <c r="Q420" s="21"/>
     </row>
-    <row r="421" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="20"/>
       <c r="B421" s="20"/>
       <c r="C421" s="20"/>
@@ -33134,7 +33138,7 @@
       <c r="P421" s="20"/>
       <c r="Q421" s="21"/>
     </row>
-    <row r="422" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="20"/>
       <c r="B422" s="20"/>
       <c r="C422" s="20"/>
@@ -33153,7 +33157,7 @@
       <c r="P422" s="20"/>
       <c r="Q422" s="21"/>
     </row>
-    <row r="423" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="20"/>
       <c r="B423" s="20"/>
       <c r="C423" s="20"/>
@@ -33172,7 +33176,7 @@
       <c r="P423" s="20"/>
       <c r="Q423" s="21"/>
     </row>
-    <row r="424" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="20"/>
       <c r="B424" s="20"/>
       <c r="C424" s="20"/>
@@ -33191,7 +33195,7 @@
       <c r="P424" s="20"/>
       <c r="Q424" s="21"/>
     </row>
-    <row r="425" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="20"/>
       <c r="B425" s="20"/>
       <c r="C425" s="20"/>
@@ -33210,7 +33214,7 @@
       <c r="P425" s="20"/>
       <c r="Q425" s="21"/>
     </row>
-    <row r="426" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="20"/>
       <c r="B426" s="20"/>
       <c r="C426" s="20"/>
@@ -33229,7 +33233,7 @@
       <c r="P426" s="20"/>
       <c r="Q426" s="21"/>
     </row>
-    <row r="427" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="20"/>
       <c r="B427" s="20"/>
       <c r="C427" s="20"/>
@@ -33248,7 +33252,7 @@
       <c r="P427" s="20"/>
       <c r="Q427" s="21"/>
     </row>
-    <row r="428" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="20"/>
       <c r="B428" s="20"/>
       <c r="C428" s="20"/>
@@ -33267,7 +33271,7 @@
       <c r="P428" s="20"/>
       <c r="Q428" s="21"/>
     </row>
-    <row r="429" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="20"/>
       <c r="B429" s="20"/>
       <c r="C429" s="20"/>
@@ -33286,7 +33290,7 @@
       <c r="P429" s="20"/>
       <c r="Q429" s="21"/>
     </row>
-    <row r="430" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="20"/>
       <c r="B430" s="20"/>
       <c r="C430" s="20"/>
@@ -33305,7 +33309,7 @@
       <c r="P430" s="20"/>
       <c r="Q430" s="21"/>
     </row>
-    <row r="431" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="20"/>
       <c r="B431" s="20"/>
       <c r="C431" s="20"/>
@@ -33324,7 +33328,7 @@
       <c r="P431" s="20"/>
       <c r="Q431" s="21"/>
     </row>
-    <row r="432" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="20"/>
       <c r="B432" s="20"/>
       <c r="C432" s="20"/>
@@ -33343,7 +33347,7 @@
       <c r="P432" s="20"/>
       <c r="Q432" s="21"/>
     </row>
-    <row r="433" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="20"/>
       <c r="B433" s="20"/>
       <c r="C433" s="20"/>
@@ -33362,7 +33366,7 @@
       <c r="P433" s="20"/>
       <c r="Q433" s="21"/>
     </row>
-    <row r="434" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="20"/>
       <c r="B434" s="20"/>
       <c r="C434" s="20"/>
@@ -33381,7 +33385,7 @@
       <c r="P434" s="20"/>
       <c r="Q434" s="21"/>
     </row>
-    <row r="435" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="20"/>
       <c r="B435" s="20"/>
       <c r="C435" s="20"/>
@@ -33400,7 +33404,7 @@
       <c r="P435" s="20"/>
       <c r="Q435" s="21"/>
     </row>
-    <row r="436" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="20"/>
       <c r="B436" s="20"/>
       <c r="C436" s="20"/>
@@ -33419,7 +33423,7 @@
       <c r="P436" s="20"/>
       <c r="Q436" s="21"/>
     </row>
-    <row r="437" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="20"/>
       <c r="B437" s="20"/>
       <c r="C437" s="20"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B47150A-54B6-4C4A-B8DF-59D1EB936594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1105356F-53AA-4898-883A-B332923BB107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -17866,51 +17866,53 @@
       </c>
     </row>
     <row r="131" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="34">
-        <v>0</v>
-      </c>
-      <c r="B131" s="34">
+      <c r="A131" s="31">
+        <v>0</v>
+      </c>
+      <c r="B131" s="31">
         <v>2</v>
       </c>
-      <c r="C131" s="34">
-        <v>1</v>
-      </c>
-      <c r="D131" s="35" t="s">
+      <c r="C131" s="31">
+        <v>1</v>
+      </c>
+      <c r="D131" s="32" t="s">
         <v>461</v>
       </c>
-      <c r="E131" s="35" t="s">
+      <c r="E131" s="32" t="s">
         <v>468</v>
       </c>
-      <c r="F131" s="35" t="s">
+      <c r="F131" s="32" t="s">
         <v>474</v>
       </c>
-      <c r="G131" s="35" t="s">
+      <c r="G131" s="32" t="s">
         <v>475</v>
       </c>
-      <c r="H131" s="35" t="s">
+      <c r="H131" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I131" s="34" t="s">
+      <c r="I131" s="31" t="s">
         <v>409</v>
       </c>
-      <c r="J131" s="34">
+      <c r="J131" s="31">
         <v>99</v>
       </c>
-      <c r="K131" s="34" t="s">
+      <c r="K131" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="L131" s="34" t="s">
+      <c r="L131" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="M131" s="35" t="s">
+      <c r="M131" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="N131" s="35" t="s">
-        <v>931</v>
-      </c>
-      <c r="O131" s="36"/>
-      <c r="P131" s="36"/>
-      <c r="Q131" s="35"/>
+      <c r="N131" s="32" t="s">
+        <v>932</v>
+      </c>
+      <c r="O131" s="33">
+        <v>1</v>
+      </c>
+      <c r="P131" s="33"/>
+      <c r="Q131" s="32"/>
       <c r="S131" s="2">
         <f t="shared" si="35"/>
         <v>0</v>
@@ -17957,7 +17959,7 @@
       </c>
       <c r="AE131" s="2">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF131" s="2">
         <f t="shared" si="31"/>
@@ -17965,7 +17967,7 @@
       </c>
       <c r="AG131" s="2">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH131" s="2">
         <f t="shared" si="33"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1105356F-53AA-4898-883A-B332923BB107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5213F65F-8AF6-47B2-83C5-4445B8A77F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
   <sheets>
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
@@ -3749,43 +3749,43 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI437"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.109375" style="2" customWidth="1"/>
-    <col min="2" max="3" width="6.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="35.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" style="2" customWidth="1"/>
-    <col min="10" max="11" width="8.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="6.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" style="2" customWidth="1"/>
+    <col min="10" max="11" width="8.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="14" customWidth="1"/>
     <col min="13" max="13" width="29" style="15" customWidth="1"/>
-    <col min="14" max="14" width="17.44140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" style="2" customWidth="1"/>
     <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.33203125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="2" customWidth="1"/>
-    <col min="22" max="27" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.28515625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="27" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.88671875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="27.33203125" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.33203125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="19.88671875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="15.109375" style="2" customWidth="1"/>
-    <col min="35" max="35" width="18.109375" style="2" customWidth="1"/>
-    <col min="36" max="16384" width="9.109375" style="3"/>
+    <col min="30" max="30" width="21.85546875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="27.28515625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.140625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="18.140625" style="2" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="17" t="s">
         <v>8</v>
       </c>
@@ -3808,7 +3808,7 @@
       <c r="K2" s="6"/>
       <c r="N2" s="22"/>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="18" t="s">
         <v>3</v>
       </c>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3868,7 +3868,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="19" t="s">
         <v>12</v>
       </c>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3941,7 +3941,7 @@
       <c r="AF5" s="12"/>
       <c r="AG5" s="12"/>
     </row>
-    <row r="6" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F6" s="2"/>
       <c r="S6" s="2" t="s">
         <v>15</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3998,7 +3998,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:35" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
         <v>707</v>
       </c>
@@ -4110,52 +4110,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34">
-        <v>0</v>
-      </c>
-      <c r="B8" s="34">
-        <v>1</v>
-      </c>
-      <c r="C8" s="34">
-        <v>1</v>
-      </c>
-      <c r="D8" s="35" t="s">
+    <row r="8" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31">
+        <v>0</v>
+      </c>
+      <c r="B8" s="31">
+        <v>1</v>
+      </c>
+      <c r="C8" s="31">
+        <v>1</v>
+      </c>
+      <c r="D8" s="32" t="s">
         <v>453</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="32" t="s">
         <v>472</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="31">
         <v>3</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="K8" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="31">
         <v>205</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="32" t="s">
         <v>878</v>
       </c>
-      <c r="N8" s="35" t="s">
-        <v>899</v>
-      </c>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="35"/>
+      <c r="N8" s="32" t="s">
+        <v>909</v>
+      </c>
+      <c r="O8" s="33">
+        <v>1</v>
+      </c>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="32"/>
       <c r="S8" s="2">
         <f>IF(J8=$S$7,1,0)</f>
         <v>0</v>
@@ -4202,7 +4204,7 @@
       </c>
       <c r="AE8" s="2">
         <f>O8*(1-P8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" s="2">
         <f t="shared" ref="AF8:AF71" si="3">+O8*P8*(1-A8)</f>
@@ -4210,7 +4212,7 @@
       </c>
       <c r="AG8" s="2">
         <f t="shared" ref="AG8:AG71" si="4">O8*(1-P8)*(1-A8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="2">
         <f t="shared" ref="AH8:AH71" si="5">+P8*(1-A8)</f>
@@ -4221,7 +4223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
         <v>0</v>
       </c>
@@ -4336,7 +4338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>0</v>
       </c>
@@ -4447,7 +4449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>0</v>
       </c>
@@ -4558,7 +4560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34">
         <v>0</v>
       </c>
@@ -4669,7 +4671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>0</v>
       </c>
@@ -4780,7 +4782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31">
         <v>0</v>
       </c>
@@ -4895,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>0</v>
       </c>
@@ -5006,7 +5008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>0</v>
       </c>
@@ -5115,7 +5117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>0</v>
       </c>
@@ -5226,7 +5228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="31">
         <v>0</v>
       </c>
@@ -5341,7 +5343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>0</v>
       </c>
@@ -5452,7 +5454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20">
         <v>0</v>
       </c>
@@ -5561,7 +5563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34">
         <v>0</v>
       </c>
@@ -5672,7 +5674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34">
         <v>0</v>
       </c>
@@ -5783,7 +5785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="31">
         <v>0</v>
       </c>
@@ -5896,7 +5898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="34">
         <v>0</v>
       </c>
@@ -6007,7 +6009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34">
         <v>0</v>
       </c>
@@ -6118,7 +6120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20">
         <v>0</v>
       </c>
@@ -6227,7 +6229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31">
         <v>0</v>
       </c>
@@ -6340,7 +6342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="31">
         <v>0</v>
       </c>
@@ -6455,7 +6457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="34">
         <v>0</v>
       </c>
@@ -6566,7 +6568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="34">
         <v>0</v>
       </c>
@@ -6677,7 +6679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="31">
         <v>0</v>
       </c>
@@ -6790,7 +6792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="34">
         <v>0</v>
       </c>
@@ -6901,7 +6903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="20">
         <v>0</v>
       </c>
@@ -7010,7 +7012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="31">
         <v>0</v>
       </c>
@@ -7125,7 +7127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="31">
         <v>0</v>
       </c>
@@ -7238,7 +7240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20">
         <v>0</v>
       </c>
@@ -7347,7 +7349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="34">
         <v>0</v>
       </c>
@@ -7458,7 +7460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="31">
         <v>0</v>
       </c>
@@ -7573,7 +7575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20">
         <v>0</v>
       </c>
@@ -7682,7 +7684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31">
         <v>0</v>
       </c>
@@ -7795,7 +7797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="34">
         <v>0</v>
       </c>
@@ -7906,7 +7908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="34">
         <v>0</v>
       </c>
@@ -8017,7 +8019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="31">
         <v>0</v>
       </c>
@@ -8130,7 +8132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="34">
         <v>0</v>
       </c>
@@ -8241,7 +8243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="31">
         <v>0</v>
       </c>
@@ -8354,7 +8356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="34">
         <v>0</v>
       </c>
@@ -8465,7 +8467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="34">
         <v>0</v>
       </c>
@@ -8576,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="34">
         <v>0</v>
       </c>
@@ -8687,7 +8689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31">
         <v>0</v>
       </c>
@@ -8800,7 +8802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="28">
         <v>0</v>
       </c>
@@ -8911,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="34">
         <v>0</v>
       </c>
@@ -9020,7 +9022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="34">
         <v>0</v>
       </c>
@@ -9131,7 +9133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="20">
         <v>0</v>
       </c>
@@ -9238,7 +9240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="34">
         <v>0</v>
       </c>
@@ -9349,7 +9351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="20">
         <v>0</v>
       </c>
@@ -9458,7 +9460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31">
         <v>0</v>
       </c>
@@ -9573,7 +9575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="34">
         <v>0</v>
       </c>
@@ -9684,7 +9686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20">
         <v>0</v>
       </c>
@@ -9793,7 +9795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="31">
         <v>0</v>
       </c>
@@ -9904,7 +9906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="31">
         <v>0</v>
       </c>
@@ -10015,7 +10017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20">
         <v>0</v>
       </c>
@@ -10124,7 +10126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="31">
         <v>0</v>
       </c>
@@ -10237,7 +10239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="31">
         <v>0</v>
       </c>
@@ -10350,7 +10352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="31">
         <v>0</v>
       </c>
@@ -10463,7 +10465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="31">
         <v>0</v>
       </c>
@@ -10576,7 +10578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="31">
         <v>0</v>
       </c>
@@ -10689,7 +10691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="31">
         <v>0</v>
       </c>
@@ -10802,7 +10804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="20">
         <v>0</v>
       </c>
@@ -10911,7 +10913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="34">
         <v>0</v>
       </c>
@@ -11022,7 +11024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="34">
         <v>0</v>
       </c>
@@ -11133,7 +11135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="20">
         <v>0</v>
       </c>
@@ -11242,7 +11244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="20">
         <v>1</v>
       </c>
@@ -11351,7 +11353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="31">
         <v>0</v>
       </c>
@@ -11466,7 +11468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="31">
         <v>0</v>
       </c>
@@ -11581,7 +11583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="31">
         <v>0</v>
       </c>
@@ -11692,7 +11694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="31">
         <v>1</v>
       </c>
@@ -11805,7 +11807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="31">
         <v>0</v>
       </c>
@@ -11916,7 +11918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="31">
         <v>0</v>
       </c>
@@ -12029,7 +12031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="31">
         <v>0</v>
       </c>
@@ -12144,7 +12146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="34">
         <v>0</v>
       </c>
@@ -12255,7 +12257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="28">
         <v>0</v>
       </c>
@@ -12366,7 +12368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="31">
         <v>0</v>
       </c>
@@ -12479,7 +12481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="34">
         <v>0</v>
       </c>
@@ -12590,7 +12592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="31">
         <v>0</v>
       </c>
@@ -12703,7 +12705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="20">
         <v>0</v>
       </c>
@@ -12810,7 +12812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="28">
         <v>0</v>
       </c>
@@ -12921,7 +12923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="20">
         <v>0</v>
       </c>
@@ -13028,7 +13030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="34">
         <v>0</v>
       </c>
@@ -13139,7 +13141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="31">
         <v>0</v>
       </c>
@@ -13252,7 +13254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="41">
         <v>0</v>
       </c>
@@ -13357,7 +13359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="20">
         <v>0</v>
       </c>
@@ -13466,7 +13468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="31">
         <v>0</v>
       </c>
@@ -13579,7 +13581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="31">
         <v>1</v>
       </c>
@@ -13692,7 +13694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="31">
         <v>1</v>
       </c>
@@ -13805,7 +13807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="31">
         <v>1</v>
       </c>
@@ -13918,7 +13920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="31">
         <v>1</v>
       </c>
@@ -14031,7 +14033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="31">
         <v>1</v>
       </c>
@@ -14144,7 +14146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="31">
         <v>0</v>
       </c>
@@ -14259,7 +14261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="31">
         <v>0</v>
       </c>
@@ -14372,7 +14374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="31">
         <v>0</v>
       </c>
@@ -14485,7 +14487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="31">
         <v>1</v>
       </c>
@@ -14598,7 +14600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="31">
         <v>1</v>
       </c>
@@ -14711,7 +14713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="31">
         <v>0</v>
       </c>
@@ -14826,7 +14828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="31">
         <v>1</v>
       </c>
@@ -14941,7 +14943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="31">
         <v>1</v>
       </c>
@@ -15056,7 +15058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="31">
         <v>1</v>
       </c>
@@ -15171,7 +15173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="34">
         <v>0</v>
       </c>
@@ -15282,7 +15284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="34">
         <v>1</v>
       </c>
@@ -15393,7 +15395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="31">
         <v>0</v>
       </c>
@@ -15504,7 +15506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="20">
         <v>0</v>
       </c>
@@ -15609,7 +15611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="34">
         <v>0</v>
       </c>
@@ -15720,7 +15722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="31">
         <v>0</v>
       </c>
@@ -15833,7 +15835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="31">
         <v>1</v>
       </c>
@@ -15944,7 +15946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="20">
         <v>0</v>
       </c>
@@ -16051,7 +16053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="31">
         <v>0</v>
       </c>
@@ -16166,7 +16168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="31">
         <v>1</v>
       </c>
@@ -16281,7 +16283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="20">
         <v>0</v>
       </c>
@@ -16390,7 +16392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="31">
         <v>0</v>
       </c>
@@ -16505,7 +16507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="31">
         <v>0</v>
       </c>
@@ -16620,7 +16622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="31">
         <v>1</v>
       </c>
@@ -16735,7 +16737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="31">
         <v>1</v>
       </c>
@@ -16850,7 +16852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="31">
         <v>1</v>
       </c>
@@ -16965,7 +16967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="31">
         <v>1</v>
       </c>
@@ -17080,7 +17082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="31">
         <v>0</v>
       </c>
@@ -17193,7 +17195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="31">
         <v>0</v>
       </c>
@@ -17304,7 +17306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="31">
         <v>0</v>
       </c>
@@ -17417,7 +17419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="31">
         <v>0</v>
       </c>
@@ -17532,7 +17534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="31">
         <v>1</v>
       </c>
@@ -17647,7 +17649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="31">
         <v>1</v>
       </c>
@@ -17762,7 +17764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="41">
         <v>0</v>
       </c>
@@ -17865,7 +17867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="31">
         <v>0</v>
       </c>
@@ -17978,7 +17980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="20">
         <v>0</v>
       </c>
@@ -18087,7 +18089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="31">
         <v>0</v>
       </c>
@@ -18194,7 +18196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="31">
         <v>0</v>
       </c>
@@ -18303,7 +18305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="31">
         <v>0</v>
       </c>
@@ -18418,7 +18420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="31">
         <v>0</v>
       </c>
@@ -18533,7 +18535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="31">
         <v>0</v>
       </c>
@@ -18646,7 +18648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="31">
         <v>1</v>
       </c>
@@ -18759,7 +18761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="31">
         <v>0</v>
       </c>
@@ -18874,7 +18876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="31">
         <v>0</v>
       </c>
@@ -18989,7 +18991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="31">
         <v>0</v>
       </c>
@@ -19104,7 +19106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="31">
         <v>0</v>
       </c>
@@ -19217,7 +19219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="31">
         <v>1</v>
       </c>
@@ -19330,7 +19332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="31">
         <v>0</v>
       </c>
@@ -19441,7 +19443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="31">
         <v>0</v>
       </c>
@@ -19556,7 +19558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="31">
         <v>0</v>
       </c>
@@ -19671,7 +19673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="31">
         <v>0</v>
       </c>
@@ -19784,7 +19786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="31">
         <v>0</v>
       </c>
@@ -19897,7 +19899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="20">
         <v>0</v>
       </c>
@@ -20006,7 +20008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="31">
         <v>0</v>
       </c>
@@ -20119,7 +20121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="34">
         <v>0</v>
       </c>
@@ -20228,7 +20230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="31">
         <v>0</v>
       </c>
@@ -20341,7 +20343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="31">
         <v>0</v>
       </c>
@@ -20456,7 +20458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="31">
         <v>1</v>
       </c>
@@ -20569,7 +20571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="31">
         <v>0</v>
       </c>
@@ -20682,7 +20684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="31">
         <v>1</v>
       </c>
@@ -20795,7 +20797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="31">
         <v>0</v>
       </c>
@@ -20908,7 +20910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="34">
         <v>0</v>
       </c>
@@ -21019,7 +21021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="28">
         <v>0</v>
       </c>
@@ -21130,7 +21132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="41">
         <v>0</v>
       </c>
@@ -21235,7 +21237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="28">
         <v>0</v>
       </c>
@@ -21338,7 +21340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="34">
         <v>0</v>
       </c>
@@ -21449,7 +21451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="31">
         <v>0</v>
       </c>
@@ -21562,7 +21564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="34">
         <v>0</v>
       </c>
@@ -21673,7 +21675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="34">
         <v>0</v>
       </c>
@@ -21784,7 +21786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="28">
         <v>0</v>
       </c>
@@ -21895,7 +21897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="31">
         <v>0</v>
       </c>
@@ -22010,7 +22012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="31">
         <v>0</v>
       </c>
@@ -22125,7 +22127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="31">
         <v>1</v>
       </c>
@@ -22240,7 +22242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="20">
         <v>0</v>
       </c>
@@ -22349,7 +22351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="31">
         <v>0</v>
       </c>
@@ -22464,7 +22466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="31">
         <v>0</v>
       </c>
@@ -22569,7 +22571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="20">
         <v>0</v>
       </c>
@@ -22678,7 +22680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="31">
         <v>0</v>
       </c>
@@ -22791,7 +22793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="31">
         <v>0</v>
       </c>
@@ -22904,7 +22906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="34">
         <v>0</v>
       </c>
@@ -23015,7 +23017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="34">
         <v>0</v>
       </c>
@@ -23126,7 +23128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="34">
         <v>1</v>
       </c>
@@ -23237,7 +23239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="34">
         <v>1</v>
       </c>
@@ -23348,7 +23350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="20">
         <v>0</v>
       </c>
@@ -23453,7 +23455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="20">
         <v>0</v>
       </c>
@@ -23562,7 +23564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="34">
         <v>0</v>
       </c>
@@ -23673,7 +23675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="20">
         <v>0</v>
       </c>
@@ -23782,7 +23784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="20">
         <v>0</v>
       </c>
@@ -23891,7 +23893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="34">
         <v>0</v>
       </c>
@@ -24002,7 +24004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="31">
         <v>0</v>
       </c>
@@ -24113,7 +24115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="34">
         <v>0</v>
       </c>
@@ -24224,7 +24226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="34">
         <v>0</v>
       </c>
@@ -24335,7 +24337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="34">
         <v>0</v>
       </c>
@@ -24446,7 +24448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="34">
         <v>0</v>
       </c>
@@ -24557,7 +24559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="34">
         <v>0</v>
       </c>
@@ -24668,7 +24670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="31">
         <v>0</v>
       </c>
@@ -24781,7 +24783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="31">
         <v>0</v>
       </c>
@@ -24896,7 +24898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="20">
         <v>0</v>
       </c>
@@ -25005,7 +25007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="34">
         <v>0</v>
       </c>
@@ -25116,7 +25118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="34">
         <v>0</v>
       </c>
@@ -25227,7 +25229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="34">
         <v>0</v>
       </c>
@@ -25338,7 +25340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="34">
         <v>0</v>
       </c>
@@ -25449,7 +25451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="34">
         <v>0</v>
       </c>
@@ -25560,7 +25562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="31">
         <v>0</v>
       </c>
@@ -25673,7 +25675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="34">
         <v>0</v>
       </c>
@@ -25784,7 +25786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="34">
         <v>0</v>
       </c>
@@ -25893,7 +25895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="31">
         <v>0</v>
       </c>
@@ -26006,7 +26008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="31">
         <v>1</v>
       </c>
@@ -26119,7 +26121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="31">
         <v>0</v>
       </c>
@@ -26234,7 +26236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="31">
         <v>0</v>
       </c>
@@ -26345,7 +26347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="31">
         <v>0</v>
       </c>
@@ -26458,7 +26460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="34">
         <v>0</v>
       </c>
@@ -26569,7 +26571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="31">
         <v>0</v>
       </c>
@@ -26684,7 +26686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="31">
         <v>0</v>
       </c>
@@ -26799,7 +26801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="31">
         <v>0</v>
       </c>
@@ -26912,7 +26914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="31">
         <v>1</v>
       </c>
@@ -27025,7 +27027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="31">
         <v>0</v>
       </c>
@@ -27138,7 +27140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="31">
         <v>0</v>
       </c>
@@ -27251,7 +27253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="31">
         <v>0</v>
       </c>
@@ -27364,7 +27366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="31">
         <v>1</v>
       </c>
@@ -27477,7 +27479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="31">
         <v>0</v>
       </c>
@@ -27590,7 +27592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="34">
         <v>0</v>
       </c>
@@ -27701,7 +27703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="34">
         <v>0</v>
       </c>
@@ -27812,7 +27814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="34">
         <v>0</v>
       </c>
@@ -27923,7 +27925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="31">
         <v>0</v>
       </c>
@@ -28036,7 +28038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="31">
         <v>0</v>
       </c>
@@ -28149,7 +28151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="31">
         <v>0</v>
       </c>
@@ -28260,7 +28262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="31">
         <v>1</v>
       </c>
@@ -28367,7 +28369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="31">
         <v>0</v>
       </c>
@@ -28480,7 +28482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="31">
         <v>1</v>
       </c>
@@ -28595,7 +28597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="31">
         <v>0</v>
       </c>
@@ -28708,7 +28710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="31">
         <v>1</v>
       </c>
@@ -28821,7 +28823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="31">
         <v>1</v>
       </c>
@@ -28934,7 +28936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="31">
         <v>0</v>
       </c>
@@ -29047,7 +29049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="31">
         <v>1</v>
       </c>
@@ -29160,7 +29162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="31">
         <v>0</v>
       </c>
@@ -29273,7 +29275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="34">
         <v>0</v>
       </c>
@@ -29384,7 +29386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="34">
         <v>1</v>
       </c>
@@ -29495,7 +29497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="34">
         <v>1</v>
       </c>
@@ -29606,7 +29608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="20"/>
       <c r="B236" s="20"/>
       <c r="C236" s="20"/>
@@ -29625,7 +29627,7 @@
       <c r="P236" s="20"/>
       <c r="Q236" s="21"/>
     </row>
-    <row r="237" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="20"/>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -29644,7 +29646,7 @@
       <c r="P237" s="20"/>
       <c r="Q237" s="21"/>
     </row>
-    <row r="238" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="20"/>
       <c r="B238" s="20"/>
       <c r="C238" s="20"/>
@@ -29663,7 +29665,7 @@
       <c r="P238" s="20"/>
       <c r="Q238" s="21"/>
     </row>
-    <row r="239" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="20"/>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -29682,7 +29684,7 @@
       <c r="P239" s="20"/>
       <c r="Q239" s="21"/>
     </row>
-    <row r="240" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="20"/>
@@ -29701,7 +29703,7 @@
       <c r="P240" s="20"/>
       <c r="Q240" s="21"/>
     </row>
-    <row r="241" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="20"/>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -29720,7 +29722,7 @@
       <c r="P241" s="20"/>
       <c r="Q241" s="21"/>
     </row>
-    <row r="242" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="20"/>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -29739,7 +29741,7 @@
       <c r="P242" s="20"/>
       <c r="Q242" s="21"/>
     </row>
-    <row r="243" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="20"/>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -29758,7 +29760,7 @@
       <c r="P243" s="20"/>
       <c r="Q243" s="21"/>
     </row>
-    <row r="244" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="20"/>
       <c r="B244" s="20"/>
       <c r="C244" s="20"/>
@@ -29777,7 +29779,7 @@
       <c r="P244" s="20"/>
       <c r="Q244" s="21"/>
     </row>
-    <row r="245" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="20"/>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -29796,7 +29798,7 @@
       <c r="P245" s="20"/>
       <c r="Q245" s="21"/>
     </row>
-    <row r="246" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="20"/>
       <c r="B246" s="20"/>
       <c r="C246" s="20"/>
@@ -29815,7 +29817,7 @@
       <c r="P246" s="20"/>
       <c r="Q246" s="21"/>
     </row>
-    <row r="247" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="20"/>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -29834,7 +29836,7 @@
       <c r="P247" s="20"/>
       <c r="Q247" s="21"/>
     </row>
-    <row r="248" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="20"/>
       <c r="B248" s="20"/>
       <c r="C248" s="20"/>
@@ -29853,7 +29855,7 @@
       <c r="P248" s="20"/>
       <c r="Q248" s="21"/>
     </row>
-    <row r="249" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="20"/>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -29872,7 +29874,7 @@
       <c r="P249" s="20"/>
       <c r="Q249" s="21"/>
     </row>
-    <row r="250" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="20"/>
       <c r="B250" s="20"/>
       <c r="C250" s="20"/>
@@ -29891,7 +29893,7 @@
       <c r="P250" s="20"/>
       <c r="Q250" s="21"/>
     </row>
-    <row r="251" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="20"/>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -29910,7 +29912,7 @@
       <c r="P251" s="20"/>
       <c r="Q251" s="21"/>
     </row>
-    <row r="252" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="20"/>
       <c r="B252" s="20"/>
       <c r="C252" s="20"/>
@@ -29929,7 +29931,7 @@
       <c r="P252" s="20"/>
       <c r="Q252" s="21"/>
     </row>
-    <row r="253" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="20"/>
       <c r="B253" s="20"/>
       <c r="C253" s="20"/>
@@ -29948,7 +29950,7 @@
       <c r="P253" s="20"/>
       <c r="Q253" s="21"/>
     </row>
-    <row r="254" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="20"/>
       <c r="B254" s="20"/>
       <c r="C254" s="20"/>
@@ -29967,7 +29969,7 @@
       <c r="P254" s="20"/>
       <c r="Q254" s="21"/>
     </row>
-    <row r="255" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="20"/>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -29986,7 +29988,7 @@
       <c r="P255" s="20"/>
       <c r="Q255" s="21"/>
     </row>
-    <row r="256" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="20"/>
       <c r="B256" s="20"/>
       <c r="C256" s="20"/>
@@ -30005,7 +30007,7 @@
       <c r="P256" s="20"/>
       <c r="Q256" s="21"/>
     </row>
-    <row r="257" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="20"/>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -30024,7 +30026,7 @@
       <c r="P257" s="20"/>
       <c r="Q257" s="21"/>
     </row>
-    <row r="258" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="20"/>
       <c r="B258" s="20"/>
       <c r="C258" s="20"/>
@@ -30043,7 +30045,7 @@
       <c r="P258" s="20"/>
       <c r="Q258" s="21"/>
     </row>
-    <row r="259" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="20"/>
       <c r="B259" s="20"/>
       <c r="C259" s="20"/>
@@ -30062,7 +30064,7 @@
       <c r="P259" s="20"/>
       <c r="Q259" s="21"/>
     </row>
-    <row r="260" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="20"/>
       <c r="B260" s="20"/>
       <c r="C260" s="20"/>
@@ -30081,7 +30083,7 @@
       <c r="P260" s="20"/>
       <c r="Q260" s="21"/>
     </row>
-    <row r="261" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="20"/>
       <c r="B261" s="20"/>
       <c r="C261" s="20"/>
@@ -30100,7 +30102,7 @@
       <c r="P261" s="20"/>
       <c r="Q261" s="21"/>
     </row>
-    <row r="262" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="20"/>
       <c r="B262" s="20"/>
       <c r="C262" s="20"/>
@@ -30119,7 +30121,7 @@
       <c r="P262" s="20"/>
       <c r="Q262" s="21"/>
     </row>
-    <row r="263" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="20"/>
       <c r="B263" s="20"/>
       <c r="C263" s="20"/>
@@ -30138,7 +30140,7 @@
       <c r="P263" s="20"/>
       <c r="Q263" s="21"/>
     </row>
-    <row r="264" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="20"/>
       <c r="B264" s="20"/>
       <c r="C264" s="20"/>
@@ -30157,7 +30159,7 @@
       <c r="P264" s="20"/>
       <c r="Q264" s="21"/>
     </row>
-    <row r="265" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="20"/>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -30176,7 +30178,7 @@
       <c r="P265" s="20"/>
       <c r="Q265" s="21"/>
     </row>
-    <row r="266" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="20"/>
       <c r="B266" s="20"/>
       <c r="C266" s="20"/>
@@ -30195,7 +30197,7 @@
       <c r="P266" s="20"/>
       <c r="Q266" s="21"/>
     </row>
-    <row r="267" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="20"/>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -30214,7 +30216,7 @@
       <c r="P267" s="20"/>
       <c r="Q267" s="21"/>
     </row>
-    <row r="268" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="20"/>
       <c r="B268" s="20"/>
       <c r="C268" s="20"/>
@@ -30233,7 +30235,7 @@
       <c r="P268" s="20"/>
       <c r="Q268" s="21"/>
     </row>
-    <row r="269" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -30252,7 +30254,7 @@
       <c r="P269" s="20"/>
       <c r="Q269" s="21"/>
     </row>
-    <row r="270" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="20"/>
       <c r="B270" s="20"/>
       <c r="C270" s="20"/>
@@ -30271,7 +30273,7 @@
       <c r="P270" s="20"/>
       <c r="Q270" s="21"/>
     </row>
-    <row r="271" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="20"/>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -30290,7 +30292,7 @@
       <c r="P271" s="20"/>
       <c r="Q271" s="21"/>
     </row>
-    <row r="272" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="20"/>
       <c r="B272" s="20"/>
       <c r="C272" s="20"/>
@@ -30309,7 +30311,7 @@
       <c r="P272" s="20"/>
       <c r="Q272" s="21"/>
     </row>
-    <row r="273" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="20"/>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -30328,7 +30330,7 @@
       <c r="P273" s="20"/>
       <c r="Q273" s="21"/>
     </row>
-    <row r="274" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="20"/>
       <c r="B274" s="20"/>
       <c r="C274" s="20"/>
@@ -30347,7 +30349,7 @@
       <c r="P274" s="20"/>
       <c r="Q274" s="21"/>
     </row>
-    <row r="275" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="20"/>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -30366,7 +30368,7 @@
       <c r="P275" s="20"/>
       <c r="Q275" s="21"/>
     </row>
-    <row r="276" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="20"/>
       <c r="B276" s="20"/>
       <c r="C276" s="20"/>
@@ -30385,7 +30387,7 @@
       <c r="P276" s="20"/>
       <c r="Q276" s="21"/>
     </row>
-    <row r="277" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="20"/>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -30404,7 +30406,7 @@
       <c r="P277" s="20"/>
       <c r="Q277" s="21"/>
     </row>
-    <row r="278" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="20"/>
       <c r="B278" s="20"/>
       <c r="C278" s="20"/>
@@ -30423,7 +30425,7 @@
       <c r="P278" s="20"/>
       <c r="Q278" s="21"/>
     </row>
-    <row r="279" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="20"/>
       <c r="B279" s="20"/>
       <c r="C279" s="20"/>
@@ -30442,7 +30444,7 @@
       <c r="P279" s="20"/>
       <c r="Q279" s="21"/>
     </row>
-    <row r="280" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20"/>
       <c r="B280" s="20"/>
       <c r="C280" s="20"/>
@@ -30461,7 +30463,7 @@
       <c r="P280" s="20"/>
       <c r="Q280" s="21"/>
     </row>
-    <row r="281" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="20"/>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -30480,7 +30482,7 @@
       <c r="P281" s="20"/>
       <c r="Q281" s="21"/>
     </row>
-    <row r="282" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20"/>
       <c r="B282" s="20"/>
       <c r="C282" s="20"/>
@@ -30499,7 +30501,7 @@
       <c r="P282" s="20"/>
       <c r="Q282" s="21"/>
     </row>
-    <row r="283" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="20"/>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -30518,7 +30520,7 @@
       <c r="P283" s="20"/>
       <c r="Q283" s="21"/>
     </row>
-    <row r="284" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="20"/>
       <c r="B284" s="20"/>
       <c r="C284" s="20"/>
@@ -30537,7 +30539,7 @@
       <c r="P284" s="20"/>
       <c r="Q284" s="21"/>
     </row>
-    <row r="285" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="20"/>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -30556,7 +30558,7 @@
       <c r="P285" s="20"/>
       <c r="Q285" s="21"/>
     </row>
-    <row r="286" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20"/>
       <c r="B286" s="20"/>
       <c r="C286" s="20"/>
@@ -30575,7 +30577,7 @@
       <c r="P286" s="20"/>
       <c r="Q286" s="21"/>
     </row>
-    <row r="287" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="20"/>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -30594,7 +30596,7 @@
       <c r="P287" s="20"/>
       <c r="Q287" s="21"/>
     </row>
-    <row r="288" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20"/>
       <c r="B288" s="20"/>
       <c r="C288" s="20"/>
@@ -30613,7 +30615,7 @@
       <c r="P288" s="20"/>
       <c r="Q288" s="21"/>
     </row>
-    <row r="289" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="20"/>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -30632,7 +30634,7 @@
       <c r="P289" s="20"/>
       <c r="Q289" s="21"/>
     </row>
-    <row r="290" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="20"/>
       <c r="B290" s="20"/>
       <c r="C290" s="20"/>
@@ -30651,7 +30653,7 @@
       <c r="P290" s="20"/>
       <c r="Q290" s="21"/>
     </row>
-    <row r="291" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="20"/>
       <c r="B291" s="20"/>
       <c r="C291" s="20"/>
@@ -30670,7 +30672,7 @@
       <c r="P291" s="20"/>
       <c r="Q291" s="21"/>
     </row>
-    <row r="292" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="20"/>
       <c r="B292" s="20"/>
       <c r="C292" s="20"/>
@@ -30689,7 +30691,7 @@
       <c r="P292" s="20"/>
       <c r="Q292" s="21"/>
     </row>
-    <row r="293" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="20"/>
       <c r="B293" s="20"/>
       <c r="C293" s="20"/>
@@ -30708,7 +30710,7 @@
       <c r="P293" s="20"/>
       <c r="Q293" s="21"/>
     </row>
-    <row r="294" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="20"/>
       <c r="B294" s="20"/>
       <c r="C294" s="20"/>
@@ -30727,7 +30729,7 @@
       <c r="P294" s="20"/>
       <c r="Q294" s="21"/>
     </row>
-    <row r="295" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="20"/>
       <c r="B295" s="20"/>
       <c r="C295" s="20"/>
@@ -30746,7 +30748,7 @@
       <c r="P295" s="20"/>
       <c r="Q295" s="21"/>
     </row>
-    <row r="296" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="20"/>
       <c r="B296" s="20"/>
       <c r="C296" s="20"/>
@@ -30765,7 +30767,7 @@
       <c r="P296" s="20"/>
       <c r="Q296" s="21"/>
     </row>
-    <row r="297" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="20"/>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -30784,7 +30786,7 @@
       <c r="P297" s="20"/>
       <c r="Q297" s="21"/>
     </row>
-    <row r="298" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="20"/>
       <c r="B298" s="20"/>
       <c r="C298" s="20"/>
@@ -30803,7 +30805,7 @@
       <c r="P298" s="20"/>
       <c r="Q298" s="21"/>
     </row>
-    <row r="299" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="20"/>
       <c r="B299" s="20"/>
       <c r="C299" s="20"/>
@@ -30822,7 +30824,7 @@
       <c r="P299" s="20"/>
       <c r="Q299" s="21"/>
     </row>
-    <row r="300" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="20"/>
       <c r="B300" s="20"/>
       <c r="C300" s="20"/>
@@ -30841,7 +30843,7 @@
       <c r="P300" s="20"/>
       <c r="Q300" s="21"/>
     </row>
-    <row r="301" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="20"/>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -30860,7 +30862,7 @@
       <c r="P301" s="20"/>
       <c r="Q301" s="21"/>
     </row>
-    <row r="302" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="20"/>
       <c r="B302" s="20"/>
       <c r="C302" s="20"/>
@@ -30879,7 +30881,7 @@
       <c r="P302" s="20"/>
       <c r="Q302" s="21"/>
     </row>
-    <row r="303" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="20"/>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -30898,7 +30900,7 @@
       <c r="P303" s="20"/>
       <c r="Q303" s="21"/>
     </row>
-    <row r="304" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="20"/>
       <c r="B304" s="20"/>
       <c r="C304" s="20"/>
@@ -30917,7 +30919,7 @@
       <c r="P304" s="20"/>
       <c r="Q304" s="21"/>
     </row>
-    <row r="305" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="20"/>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -30936,7 +30938,7 @@
       <c r="P305" s="20"/>
       <c r="Q305" s="21"/>
     </row>
-    <row r="306" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="20"/>
       <c r="B306" s="20"/>
       <c r="C306" s="20"/>
@@ -30955,7 +30957,7 @@
       <c r="P306" s="20"/>
       <c r="Q306" s="21"/>
     </row>
-    <row r="307" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="20"/>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -30974,7 +30976,7 @@
       <c r="P307" s="20"/>
       <c r="Q307" s="21"/>
     </row>
-    <row r="308" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="20"/>
       <c r="B308" s="20"/>
       <c r="C308" s="20"/>
@@ -30993,7 +30995,7 @@
       <c r="P308" s="20"/>
       <c r="Q308" s="21"/>
     </row>
-    <row r="309" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="20"/>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -31012,7 +31014,7 @@
       <c r="P309" s="20"/>
       <c r="Q309" s="21"/>
     </row>
-    <row r="310" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="20"/>
       <c r="B310" s="20"/>
       <c r="C310" s="20"/>
@@ -31031,7 +31033,7 @@
       <c r="P310" s="20"/>
       <c r="Q310" s="21"/>
     </row>
-    <row r="311" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="20"/>
       <c r="B311" s="20"/>
       <c r="C311" s="20"/>
@@ -31050,7 +31052,7 @@
       <c r="P311" s="20"/>
       <c r="Q311" s="21"/>
     </row>
-    <row r="312" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="20"/>
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
@@ -31069,7 +31071,7 @@
       <c r="P312" s="20"/>
       <c r="Q312" s="21"/>
     </row>
-    <row r="313" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="20"/>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -31088,7 +31090,7 @@
       <c r="P313" s="20"/>
       <c r="Q313" s="21"/>
     </row>
-    <row r="314" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="20"/>
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
@@ -31107,7 +31109,7 @@
       <c r="P314" s="20"/>
       <c r="Q314" s="21"/>
     </row>
-    <row r="315" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="20"/>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -31126,7 +31128,7 @@
       <c r="P315" s="20"/>
       <c r="Q315" s="21"/>
     </row>
-    <row r="316" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="20"/>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>
@@ -31145,7 +31147,7 @@
       <c r="P316" s="20"/>
       <c r="Q316" s="21"/>
     </row>
-    <row r="317" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="20"/>
       <c r="B317" s="20"/>
       <c r="C317" s="20"/>
@@ -31164,7 +31166,7 @@
       <c r="P317" s="20"/>
       <c r="Q317" s="21"/>
     </row>
-    <row r="318" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="20"/>
       <c r="B318" s="20"/>
       <c r="C318" s="20"/>
@@ -31183,7 +31185,7 @@
       <c r="P318" s="20"/>
       <c r="Q318" s="21"/>
     </row>
-    <row r="319" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="20"/>
       <c r="B319" s="20"/>
       <c r="C319" s="20"/>
@@ -31202,7 +31204,7 @@
       <c r="P319" s="20"/>
       <c r="Q319" s="21"/>
     </row>
-    <row r="320" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="20"/>
       <c r="B320" s="20"/>
       <c r="C320" s="20"/>
@@ -31221,7 +31223,7 @@
       <c r="P320" s="20"/>
       <c r="Q320" s="21"/>
     </row>
-    <row r="321" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="20"/>
       <c r="B321" s="20"/>
       <c r="C321" s="20"/>
@@ -31240,7 +31242,7 @@
       <c r="P321" s="20"/>
       <c r="Q321" s="21"/>
     </row>
-    <row r="322" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="20"/>
       <c r="B322" s="20"/>
       <c r="C322" s="20"/>
@@ -31259,7 +31261,7 @@
       <c r="P322" s="20"/>
       <c r="Q322" s="21"/>
     </row>
-    <row r="323" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="20"/>
       <c r="B323" s="20"/>
       <c r="C323" s="20"/>
@@ -31278,7 +31280,7 @@
       <c r="P323" s="20"/>
       <c r="Q323" s="21"/>
     </row>
-    <row r="324" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="20"/>
       <c r="B324" s="20"/>
       <c r="C324" s="20"/>
@@ -31297,7 +31299,7 @@
       <c r="P324" s="20"/>
       <c r="Q324" s="21"/>
     </row>
-    <row r="325" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="20"/>
       <c r="B325" s="20"/>
       <c r="C325" s="20"/>
@@ -31316,7 +31318,7 @@
       <c r="P325" s="20"/>
       <c r="Q325" s="21"/>
     </row>
-    <row r="326" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="20"/>
       <c r="B326" s="20"/>
       <c r="C326" s="20"/>
@@ -31335,7 +31337,7 @@
       <c r="P326" s="20"/>
       <c r="Q326" s="21"/>
     </row>
-    <row r="327" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="20"/>
       <c r="B327" s="20"/>
       <c r="C327" s="20"/>
@@ -31354,7 +31356,7 @@
       <c r="P327" s="20"/>
       <c r="Q327" s="21"/>
     </row>
-    <row r="328" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="20"/>
       <c r="B328" s="20"/>
       <c r="C328" s="20"/>
@@ -31373,7 +31375,7 @@
       <c r="P328" s="20"/>
       <c r="Q328" s="21"/>
     </row>
-    <row r="329" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="20"/>
       <c r="B329" s="20"/>
       <c r="C329" s="20"/>
@@ -31392,7 +31394,7 @@
       <c r="P329" s="20"/>
       <c r="Q329" s="21"/>
     </row>
-    <row r="330" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="20"/>
       <c r="B330" s="20"/>
       <c r="C330" s="20"/>
@@ -31411,7 +31413,7 @@
       <c r="P330" s="20"/>
       <c r="Q330" s="21"/>
     </row>
-    <row r="331" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="20"/>
       <c r="B331" s="20"/>
       <c r="C331" s="20"/>
@@ -31430,7 +31432,7 @@
       <c r="P331" s="20"/>
       <c r="Q331" s="21"/>
     </row>
-    <row r="332" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="20"/>
       <c r="B332" s="20"/>
       <c r="C332" s="20"/>
@@ -31449,7 +31451,7 @@
       <c r="P332" s="20"/>
       <c r="Q332" s="21"/>
     </row>
-    <row r="333" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="20"/>
       <c r="B333" s="20"/>
       <c r="C333" s="20"/>
@@ -31468,7 +31470,7 @@
       <c r="P333" s="20"/>
       <c r="Q333" s="21"/>
     </row>
-    <row r="334" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="20"/>
       <c r="B334" s="20"/>
       <c r="C334" s="20"/>
@@ -31487,7 +31489,7 @@
       <c r="P334" s="20"/>
       <c r="Q334" s="21"/>
     </row>
-    <row r="335" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="20"/>
       <c r="B335" s="20"/>
       <c r="C335" s="20"/>
@@ -31506,7 +31508,7 @@
       <c r="P335" s="20"/>
       <c r="Q335" s="21"/>
     </row>
-    <row r="336" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="20"/>
       <c r="B336" s="20"/>
       <c r="C336" s="20"/>
@@ -31525,7 +31527,7 @@
       <c r="P336" s="20"/>
       <c r="Q336" s="21"/>
     </row>
-    <row r="337" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="20"/>
       <c r="B337" s="20"/>
       <c r="C337" s="20"/>
@@ -31544,7 +31546,7 @@
       <c r="P337" s="20"/>
       <c r="Q337" s="21"/>
     </row>
-    <row r="338" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="20"/>
       <c r="B338" s="20"/>
       <c r="C338" s="20"/>
@@ -31563,7 +31565,7 @@
       <c r="P338" s="20"/>
       <c r="Q338" s="21"/>
     </row>
-    <row r="339" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="20"/>
       <c r="B339" s="20"/>
       <c r="C339" s="20"/>
@@ -31582,7 +31584,7 @@
       <c r="P339" s="20"/>
       <c r="Q339" s="21"/>
     </row>
-    <row r="340" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="20"/>
       <c r="B340" s="20"/>
       <c r="C340" s="20"/>
@@ -31601,7 +31603,7 @@
       <c r="P340" s="20"/>
       <c r="Q340" s="21"/>
     </row>
-    <row r="341" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="20"/>
       <c r="B341" s="20"/>
       <c r="C341" s="20"/>
@@ -31620,7 +31622,7 @@
       <c r="P341" s="20"/>
       <c r="Q341" s="21"/>
     </row>
-    <row r="342" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="20"/>
       <c r="B342" s="20"/>
       <c r="C342" s="20"/>
@@ -31639,7 +31641,7 @@
       <c r="P342" s="20"/>
       <c r="Q342" s="21"/>
     </row>
-    <row r="343" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="20"/>
       <c r="B343" s="20"/>
       <c r="C343" s="20"/>
@@ -31658,7 +31660,7 @@
       <c r="P343" s="20"/>
       <c r="Q343" s="21"/>
     </row>
-    <row r="344" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="20"/>
       <c r="B344" s="20"/>
       <c r="C344" s="20"/>
@@ -31677,7 +31679,7 @@
       <c r="P344" s="20"/>
       <c r="Q344" s="21"/>
     </row>
-    <row r="345" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="20"/>
       <c r="B345" s="20"/>
       <c r="C345" s="20"/>
@@ -31696,7 +31698,7 @@
       <c r="P345" s="20"/>
       <c r="Q345" s="21"/>
     </row>
-    <row r="346" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="20"/>
       <c r="B346" s="20"/>
       <c r="C346" s="20"/>
@@ -31715,7 +31717,7 @@
       <c r="P346" s="20"/>
       <c r="Q346" s="21"/>
     </row>
-    <row r="347" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="20"/>
       <c r="B347" s="20"/>
       <c r="C347" s="20"/>
@@ -31734,7 +31736,7 @@
       <c r="P347" s="20"/>
       <c r="Q347" s="21"/>
     </row>
-    <row r="348" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="20"/>
       <c r="B348" s="20"/>
       <c r="C348" s="20"/>
@@ -31753,7 +31755,7 @@
       <c r="P348" s="20"/>
       <c r="Q348" s="21"/>
     </row>
-    <row r="349" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="20"/>
       <c r="B349" s="20"/>
       <c r="C349" s="20"/>
@@ -31772,7 +31774,7 @@
       <c r="P349" s="20"/>
       <c r="Q349" s="21"/>
     </row>
-    <row r="350" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="20"/>
       <c r="B350" s="20"/>
       <c r="C350" s="20"/>
@@ -31791,7 +31793,7 @@
       <c r="P350" s="20"/>
       <c r="Q350" s="21"/>
     </row>
-    <row r="351" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="20"/>
       <c r="B351" s="20"/>
       <c r="C351" s="20"/>
@@ -31810,7 +31812,7 @@
       <c r="P351" s="20"/>
       <c r="Q351" s="21"/>
     </row>
-    <row r="352" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="20"/>
       <c r="B352" s="20"/>
       <c r="C352" s="20"/>
@@ -31829,7 +31831,7 @@
       <c r="P352" s="20"/>
       <c r="Q352" s="21"/>
     </row>
-    <row r="353" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="20"/>
       <c r="B353" s="20"/>
       <c r="C353" s="20"/>
@@ -31848,7 +31850,7 @@
       <c r="P353" s="20"/>
       <c r="Q353" s="21"/>
     </row>
-    <row r="354" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="20"/>
       <c r="B354" s="20"/>
       <c r="C354" s="20"/>
@@ -31867,7 +31869,7 @@
       <c r="P354" s="20"/>
       <c r="Q354" s="21"/>
     </row>
-    <row r="355" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="20"/>
       <c r="B355" s="20"/>
       <c r="C355" s="20"/>
@@ -31886,7 +31888,7 @@
       <c r="P355" s="20"/>
       <c r="Q355" s="21"/>
     </row>
-    <row r="356" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="20"/>
       <c r="B356" s="20"/>
       <c r="C356" s="20"/>
@@ -31905,7 +31907,7 @@
       <c r="P356" s="20"/>
       <c r="Q356" s="21"/>
     </row>
-    <row r="357" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="20"/>
       <c r="B357" s="20"/>
       <c r="C357" s="20"/>
@@ -31924,7 +31926,7 @@
       <c r="P357" s="20"/>
       <c r="Q357" s="21"/>
     </row>
-    <row r="358" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="20"/>
       <c r="B358" s="20"/>
       <c r="C358" s="20"/>
@@ -31943,7 +31945,7 @@
       <c r="P358" s="20"/>
       <c r="Q358" s="21"/>
     </row>
-    <row r="359" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="20"/>
       <c r="B359" s="20"/>
       <c r="C359" s="20"/>
@@ -31962,7 +31964,7 @@
       <c r="P359" s="20"/>
       <c r="Q359" s="21"/>
     </row>
-    <row r="360" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="20"/>
       <c r="B360" s="20"/>
       <c r="C360" s="20"/>
@@ -31981,7 +31983,7 @@
       <c r="P360" s="20"/>
       <c r="Q360" s="21"/>
     </row>
-    <row r="361" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="20"/>
       <c r="B361" s="20"/>
       <c r="C361" s="20"/>
@@ -32000,7 +32002,7 @@
       <c r="P361" s="20"/>
       <c r="Q361" s="21"/>
     </row>
-    <row r="362" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="20"/>
       <c r="B362" s="20"/>
       <c r="C362" s="20"/>
@@ -32019,7 +32021,7 @@
       <c r="P362" s="20"/>
       <c r="Q362" s="21"/>
     </row>
-    <row r="363" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="20"/>
       <c r="B363" s="20"/>
       <c r="C363" s="20"/>
@@ -32038,7 +32040,7 @@
       <c r="P363" s="20"/>
       <c r="Q363" s="21"/>
     </row>
-    <row r="364" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="20"/>
       <c r="B364" s="20"/>
       <c r="C364" s="20"/>
@@ -32057,7 +32059,7 @@
       <c r="P364" s="20"/>
       <c r="Q364" s="21"/>
     </row>
-    <row r="365" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="20"/>
       <c r="B365" s="20"/>
       <c r="C365" s="20"/>
@@ -32076,7 +32078,7 @@
       <c r="P365" s="20"/>
       <c r="Q365" s="21"/>
     </row>
-    <row r="366" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="20"/>
       <c r="B366" s="20"/>
       <c r="C366" s="20"/>
@@ -32095,7 +32097,7 @@
       <c r="P366" s="20"/>
       <c r="Q366" s="21"/>
     </row>
-    <row r="367" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="20"/>
       <c r="B367" s="20"/>
       <c r="C367" s="20"/>
@@ -32114,7 +32116,7 @@
       <c r="P367" s="20"/>
       <c r="Q367" s="21"/>
     </row>
-    <row r="368" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="20"/>
       <c r="B368" s="20"/>
       <c r="C368" s="20"/>
@@ -32133,7 +32135,7 @@
       <c r="P368" s="20"/>
       <c r="Q368" s="21"/>
     </row>
-    <row r="369" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="20"/>
       <c r="B369" s="20"/>
       <c r="C369" s="20"/>
@@ -32152,7 +32154,7 @@
       <c r="P369" s="20"/>
       <c r="Q369" s="21"/>
     </row>
-    <row r="370" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="20"/>
       <c r="B370" s="20"/>
       <c r="C370" s="20"/>
@@ -32171,7 +32173,7 @@
       <c r="P370" s="20"/>
       <c r="Q370" s="21"/>
     </row>
-    <row r="371" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="20"/>
       <c r="B371" s="20"/>
       <c r="C371" s="20"/>
@@ -32190,7 +32192,7 @@
       <c r="P371" s="20"/>
       <c r="Q371" s="21"/>
     </row>
-    <row r="372" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="20"/>
       <c r="B372" s="20"/>
       <c r="C372" s="20"/>
@@ -32209,7 +32211,7 @@
       <c r="P372" s="20"/>
       <c r="Q372" s="21"/>
     </row>
-    <row r="373" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="20"/>
       <c r="B373" s="20"/>
       <c r="C373" s="20"/>
@@ -32228,7 +32230,7 @@
       <c r="P373" s="20"/>
       <c r="Q373" s="21"/>
     </row>
-    <row r="374" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="20"/>
       <c r="B374" s="20"/>
       <c r="C374" s="20"/>
@@ -32247,7 +32249,7 @@
       <c r="P374" s="20"/>
       <c r="Q374" s="21"/>
     </row>
-    <row r="375" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="20"/>
       <c r="B375" s="20"/>
       <c r="C375" s="20"/>
@@ -32266,7 +32268,7 @@
       <c r="P375" s="20"/>
       <c r="Q375" s="21"/>
     </row>
-    <row r="376" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="20"/>
       <c r="B376" s="20"/>
       <c r="C376" s="20"/>
@@ -32285,7 +32287,7 @@
       <c r="P376" s="20"/>
       <c r="Q376" s="21"/>
     </row>
-    <row r="377" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="20"/>
       <c r="B377" s="20"/>
       <c r="C377" s="20"/>
@@ -32304,7 +32306,7 @@
       <c r="P377" s="20"/>
       <c r="Q377" s="21"/>
     </row>
-    <row r="378" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="20"/>
       <c r="B378" s="20"/>
       <c r="C378" s="20"/>
@@ -32323,7 +32325,7 @@
       <c r="P378" s="20"/>
       <c r="Q378" s="21"/>
     </row>
-    <row r="379" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="20"/>
       <c r="B379" s="20"/>
       <c r="C379" s="20"/>
@@ -32342,7 +32344,7 @@
       <c r="P379" s="20"/>
       <c r="Q379" s="21"/>
     </row>
-    <row r="380" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="20"/>
       <c r="B380" s="20"/>
       <c r="C380" s="20"/>
@@ -32361,7 +32363,7 @@
       <c r="P380" s="20"/>
       <c r="Q380" s="21"/>
     </row>
-    <row r="381" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="20"/>
       <c r="B381" s="20"/>
       <c r="C381" s="20"/>
@@ -32380,7 +32382,7 @@
       <c r="P381" s="20"/>
       <c r="Q381" s="21"/>
     </row>
-    <row r="382" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="20"/>
       <c r="B382" s="20"/>
       <c r="C382" s="20"/>
@@ -32399,7 +32401,7 @@
       <c r="P382" s="20"/>
       <c r="Q382" s="21"/>
     </row>
-    <row r="383" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="20"/>
       <c r="B383" s="20"/>
       <c r="C383" s="20"/>
@@ -32418,7 +32420,7 @@
       <c r="P383" s="20"/>
       <c r="Q383" s="21"/>
     </row>
-    <row r="384" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="20"/>
       <c r="B384" s="20"/>
       <c r="C384" s="20"/>
@@ -32437,7 +32439,7 @@
       <c r="P384" s="20"/>
       <c r="Q384" s="21"/>
     </row>
-    <row r="385" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="20"/>
       <c r="B385" s="20"/>
       <c r="C385" s="20"/>
@@ -32456,7 +32458,7 @@
       <c r="P385" s="20"/>
       <c r="Q385" s="21"/>
     </row>
-    <row r="386" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="20"/>
       <c r="B386" s="20"/>
       <c r="C386" s="20"/>
@@ -32475,7 +32477,7 @@
       <c r="P386" s="20"/>
       <c r="Q386" s="21"/>
     </row>
-    <row r="387" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="20"/>
       <c r="B387" s="20"/>
       <c r="C387" s="20"/>
@@ -32494,7 +32496,7 @@
       <c r="P387" s="20"/>
       <c r="Q387" s="21"/>
     </row>
-    <row r="388" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="20"/>
       <c r="B388" s="20"/>
       <c r="C388" s="20"/>
@@ -32513,7 +32515,7 @@
       <c r="P388" s="20"/>
       <c r="Q388" s="21"/>
     </row>
-    <row r="389" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="20"/>
       <c r="B389" s="20"/>
       <c r="C389" s="20"/>
@@ -32532,7 +32534,7 @@
       <c r="P389" s="20"/>
       <c r="Q389" s="21"/>
     </row>
-    <row r="390" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="20"/>
       <c r="B390" s="20"/>
       <c r="C390" s="20"/>
@@ -32551,7 +32553,7 @@
       <c r="P390" s="20"/>
       <c r="Q390" s="21"/>
     </row>
-    <row r="391" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="20"/>
       <c r="B391" s="20"/>
       <c r="C391" s="20"/>
@@ -32570,7 +32572,7 @@
       <c r="P391" s="20"/>
       <c r="Q391" s="21"/>
     </row>
-    <row r="392" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="20"/>
       <c r="B392" s="20"/>
       <c r="C392" s="20"/>
@@ -32589,7 +32591,7 @@
       <c r="P392" s="20"/>
       <c r="Q392" s="21"/>
     </row>
-    <row r="393" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="20"/>
       <c r="B393" s="20"/>
       <c r="C393" s="20"/>
@@ -32608,7 +32610,7 @@
       <c r="P393" s="20"/>
       <c r="Q393" s="21"/>
     </row>
-    <row r="394" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="20"/>
       <c r="B394" s="20"/>
       <c r="C394" s="20"/>
@@ -32627,7 +32629,7 @@
       <c r="P394" s="20"/>
       <c r="Q394" s="21"/>
     </row>
-    <row r="395" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="20"/>
       <c r="B395" s="20"/>
       <c r="C395" s="20"/>
@@ -32646,7 +32648,7 @@
       <c r="P395" s="20"/>
       <c r="Q395" s="21"/>
     </row>
-    <row r="396" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="20"/>
       <c r="B396" s="20"/>
       <c r="C396" s="20"/>
@@ -32665,7 +32667,7 @@
       <c r="P396" s="20"/>
       <c r="Q396" s="21"/>
     </row>
-    <row r="397" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="20"/>
       <c r="B397" s="20"/>
       <c r="C397" s="20"/>
@@ -32684,7 +32686,7 @@
       <c r="P397" s="20"/>
       <c r="Q397" s="21"/>
     </row>
-    <row r="398" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="20"/>
       <c r="B398" s="20"/>
       <c r="C398" s="20"/>
@@ -32703,7 +32705,7 @@
       <c r="P398" s="20"/>
       <c r="Q398" s="21"/>
     </row>
-    <row r="399" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="20"/>
       <c r="B399" s="20"/>
       <c r="C399" s="20"/>
@@ -32722,7 +32724,7 @@
       <c r="P399" s="20"/>
       <c r="Q399" s="21"/>
     </row>
-    <row r="400" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="20"/>
       <c r="B400" s="20"/>
       <c r="C400" s="20"/>
@@ -32741,7 +32743,7 @@
       <c r="P400" s="20"/>
       <c r="Q400" s="21"/>
     </row>
-    <row r="401" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="20"/>
       <c r="B401" s="20"/>
       <c r="C401" s="20"/>
@@ -32760,7 +32762,7 @@
       <c r="P401" s="20"/>
       <c r="Q401" s="21"/>
     </row>
-    <row r="402" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="20"/>
       <c r="B402" s="20"/>
       <c r="C402" s="20"/>
@@ -32779,7 +32781,7 @@
       <c r="P402" s="20"/>
       <c r="Q402" s="21"/>
     </row>
-    <row r="403" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="20"/>
       <c r="B403" s="20"/>
       <c r="C403" s="20"/>
@@ -32798,7 +32800,7 @@
       <c r="P403" s="20"/>
       <c r="Q403" s="21"/>
     </row>
-    <row r="404" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="20"/>
       <c r="B404" s="20"/>
       <c r="C404" s="20"/>
@@ -32817,7 +32819,7 @@
       <c r="P404" s="20"/>
       <c r="Q404" s="21"/>
     </row>
-    <row r="405" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="20"/>
       <c r="B405" s="20"/>
       <c r="C405" s="20"/>
@@ -32836,7 +32838,7 @@
       <c r="P405" s="20"/>
       <c r="Q405" s="21"/>
     </row>
-    <row r="406" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="20"/>
       <c r="B406" s="20"/>
       <c r="C406" s="20"/>
@@ -32855,7 +32857,7 @@
       <c r="P406" s="20"/>
       <c r="Q406" s="21"/>
     </row>
-    <row r="407" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="20"/>
       <c r="B407" s="20"/>
       <c r="C407" s="20"/>
@@ -32874,7 +32876,7 @@
       <c r="P407" s="20"/>
       <c r="Q407" s="21"/>
     </row>
-    <row r="408" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="20"/>
       <c r="B408" s="20"/>
       <c r="C408" s="20"/>
@@ -32893,7 +32895,7 @@
       <c r="P408" s="20"/>
       <c r="Q408" s="21"/>
     </row>
-    <row r="409" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="20"/>
       <c r="B409" s="20"/>
       <c r="C409" s="20"/>
@@ -32912,7 +32914,7 @@
       <c r="P409" s="20"/>
       <c r="Q409" s="21"/>
     </row>
-    <row r="410" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="20"/>
       <c r="B410" s="20"/>
       <c r="C410" s="20"/>
@@ -32931,7 +32933,7 @@
       <c r="P410" s="20"/>
       <c r="Q410" s="21"/>
     </row>
-    <row r="411" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="20"/>
       <c r="B411" s="20"/>
       <c r="C411" s="20"/>
@@ -32950,7 +32952,7 @@
       <c r="P411" s="20"/>
       <c r="Q411" s="21"/>
     </row>
-    <row r="412" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="20"/>
       <c r="B412" s="20"/>
       <c r="C412" s="20"/>
@@ -32969,7 +32971,7 @@
       <c r="P412" s="20"/>
       <c r="Q412" s="21"/>
     </row>
-    <row r="413" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="20"/>
       <c r="B413" s="20"/>
       <c r="C413" s="20"/>
@@ -32988,7 +32990,7 @@
       <c r="P413" s="20"/>
       <c r="Q413" s="21"/>
     </row>
-    <row r="414" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="20"/>
       <c r="B414" s="20"/>
       <c r="C414" s="20"/>
@@ -33007,7 +33009,7 @@
       <c r="P414" s="20"/>
       <c r="Q414" s="21"/>
     </row>
-    <row r="415" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="20"/>
       <c r="B415" s="20"/>
       <c r="C415" s="20"/>
@@ -33026,7 +33028,7 @@
       <c r="P415" s="20"/>
       <c r="Q415" s="21"/>
     </row>
-    <row r="416" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="20"/>
       <c r="B416" s="20"/>
       <c r="C416" s="20"/>
@@ -33045,7 +33047,7 @@
       <c r="P416" s="20"/>
       <c r="Q416" s="21"/>
     </row>
-    <row r="417" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="20"/>
       <c r="B417" s="20"/>
       <c r="C417" s="20"/>
@@ -33064,7 +33066,7 @@
       <c r="P417" s="20"/>
       <c r="Q417" s="21"/>
     </row>
-    <row r="418" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="20"/>
       <c r="B418" s="20"/>
       <c r="C418" s="20"/>
@@ -33083,7 +33085,7 @@
       <c r="P418" s="20"/>
       <c r="Q418" s="21"/>
     </row>
-    <row r="419" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="20"/>
       <c r="B419" s="20"/>
       <c r="C419" s="20"/>
@@ -33102,7 +33104,7 @@
       <c r="P419" s="20"/>
       <c r="Q419" s="21"/>
     </row>
-    <row r="420" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="20"/>
       <c r="B420" s="20"/>
       <c r="C420" s="20"/>
@@ -33121,7 +33123,7 @@
       <c r="P420" s="20"/>
       <c r="Q420" s="21"/>
     </row>
-    <row r="421" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="20"/>
       <c r="B421" s="20"/>
       <c r="C421" s="20"/>
@@ -33140,7 +33142,7 @@
       <c r="P421" s="20"/>
       <c r="Q421" s="21"/>
     </row>
-    <row r="422" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="20"/>
       <c r="B422" s="20"/>
       <c r="C422" s="20"/>
@@ -33159,7 +33161,7 @@
       <c r="P422" s="20"/>
       <c r="Q422" s="21"/>
     </row>
-    <row r="423" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="20"/>
       <c r="B423" s="20"/>
       <c r="C423" s="20"/>
@@ -33178,7 +33180,7 @@
       <c r="P423" s="20"/>
       <c r="Q423" s="21"/>
     </row>
-    <row r="424" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="20"/>
       <c r="B424" s="20"/>
       <c r="C424" s="20"/>
@@ -33197,7 +33199,7 @@
       <c r="P424" s="20"/>
       <c r="Q424" s="21"/>
     </row>
-    <row r="425" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="20"/>
       <c r="B425" s="20"/>
       <c r="C425" s="20"/>
@@ -33216,7 +33218,7 @@
       <c r="P425" s="20"/>
       <c r="Q425" s="21"/>
     </row>
-    <row r="426" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="20"/>
       <c r="B426" s="20"/>
       <c r="C426" s="20"/>
@@ -33235,7 +33237,7 @@
       <c r="P426" s="20"/>
       <c r="Q426" s="21"/>
     </row>
-    <row r="427" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="20"/>
       <c r="B427" s="20"/>
       <c r="C427" s="20"/>
@@ -33254,7 +33256,7 @@
       <c r="P427" s="20"/>
       <c r="Q427" s="21"/>
     </row>
-    <row r="428" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="20"/>
       <c r="B428" s="20"/>
       <c r="C428" s="20"/>
@@ -33273,7 +33275,7 @@
       <c r="P428" s="20"/>
       <c r="Q428" s="21"/>
     </row>
-    <row r="429" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="20"/>
       <c r="B429" s="20"/>
       <c r="C429" s="20"/>
@@ -33292,7 +33294,7 @@
       <c r="P429" s="20"/>
       <c r="Q429" s="21"/>
     </row>
-    <row r="430" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="20"/>
       <c r="B430" s="20"/>
       <c r="C430" s="20"/>
@@ -33311,7 +33313,7 @@
       <c r="P430" s="20"/>
       <c r="Q430" s="21"/>
     </row>
-    <row r="431" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="20"/>
       <c r="B431" s="20"/>
       <c r="C431" s="20"/>
@@ -33330,7 +33332,7 @@
       <c r="P431" s="20"/>
       <c r="Q431" s="21"/>
     </row>
-    <row r="432" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="20"/>
       <c r="B432" s="20"/>
       <c r="C432" s="20"/>
@@ -33349,7 +33351,7 @@
       <c r="P432" s="20"/>
       <c r="Q432" s="21"/>
     </row>
-    <row r="433" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="20"/>
       <c r="B433" s="20"/>
       <c r="C433" s="20"/>
@@ -33368,7 +33370,7 @@
       <c r="P433" s="20"/>
       <c r="Q433" s="21"/>
     </row>
-    <row r="434" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="20"/>
       <c r="B434" s="20"/>
       <c r="C434" s="20"/>
@@ -33387,7 +33389,7 @@
       <c r="P434" s="20"/>
       <c r="Q434" s="21"/>
     </row>
-    <row r="435" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="20"/>
       <c r="B435" s="20"/>
       <c r="C435" s="20"/>
@@ -33406,7 +33408,7 @@
       <c r="P435" s="20"/>
       <c r="Q435" s="21"/>
     </row>
-    <row r="436" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="20"/>
       <c r="B436" s="20"/>
       <c r="C436" s="20"/>
@@ -33425,7 +33427,7 @@
       <c r="P436" s="20"/>
       <c r="Q436" s="21"/>
     </row>
-    <row r="437" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="20"/>
       <c r="B437" s="20"/>
       <c r="C437" s="20"/>

--- a/Milano_2027.xlsx
+++ b/Milano_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5213F65F-8AF6-47B2-83C5-4445B8A77F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828EE2E7-3168-4734-8D76-854B13C4755C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{0118EB4B-1337-43BA-A7E3-0EBAC20BAF10}"/>
   </bookViews>
@@ -3848,15 +3848,15 @@
       </c>
       <c r="F4" s="9">
         <f>+AE6</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" s="9">
         <f>+AG6</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>16</v>
@@ -3878,15 +3878,15 @@
       </c>
       <c r="F5" s="11">
         <f>+F3+F4</f>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G5" s="11">
         <f>+G3+G4</f>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H5" s="11">
         <f>+H3+H4</f>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>43</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -7909,51 +7909,53 @@
       </c>
     </row>
     <row r="42" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="34">
-        <v>0</v>
-      </c>
-      <c r="B42" s="34">
-        <v>1</v>
-      </c>
-      <c r="C42" s="34">
+      <c r="A42" s="31">
+        <v>0</v>
+      </c>
+      <c r="B42" s="31">
+        <v>1</v>
+      </c>
+      <c r="C42" s="31">
         <v>3</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="32" t="s">
         <v>756</v>
       </c>
-      <c r="E42" s="35" t="s">
+      <c r="E42" s="32" t="s">
         <v>757</v>
       </c>
-      <c r="F42" s="35" t="s">
+      <c r="F42" s="32" t="s">
         <v>758</v>
       </c>
-      <c r="G42" s="35" t="s">
+      <c r="G42" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="H42" s="35" t="s">
+      <c r="H42" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="I42" s="34" t="s">
+      <c r="I42" s="31" t="s">
         <v>759</v>
       </c>
-      <c r="J42" s="34">
-        <v>1</v>
-      </c>
-      <c r="K42" s="34" t="s">
+      <c r="J42" s="31">
+        <v>1</v>
+      </c>
+      <c r="K42" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="31">
         <v>35</v>
       </c>
-      <c r="M42" s="35" t="s">
+      <c r="M42" s="32" t="s">
         <v>760</v>
       </c>
-      <c r="N42" s="35" t="s">
-        <v>902</v>
-      </c>
-      <c r="O42" s="36"/>
-      <c r="P42" s="36"/>
-      <c r="Q42" s="35"/>
+      <c r="N42" s="32" t="s">
+        <v>903</v>
+      </c>
+      <c r="O42" s="33">
+        <v>1</v>
+      </c>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="32"/>
       <c r="S42" s="2">
         <f t="shared" si="19"/>
         <v>1</v>
@@ -8000,7 +8002,7 @@
       </c>
       <c r="AE42" s="2">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF42" s="2">
         <f t="shared" si="3"/>
@@ -8008,7 +8010,7 @@
       </c>
       <c r="AG42" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42" s="2">
         <f t="shared" si="5"/>
